--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M282"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>HSV6.010</t>
+          <t>HSV6.011</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>HSV6.011</t>
+          <t>HSV6.012</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6846,30 +6846,30 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>12</v>
+        <v>56.5</v>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>HSV6.012</t>
+          <t>HSV7.001</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6895,40 +6895,40 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>56.5</v>
+        <v>276.7</v>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
@@ -6936,7 +6936,11 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6944,7 +6948,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>HSV7.001</t>
+          <t>HSV7.002a</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6975,29 +6979,28 @@
       <c r="H108" s="2" t="n">
         <v>276.7</v>
       </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
-        </is>
+      <c r="I108" s="3">
+        <f> HSV7.002 plocha fasády 276.7 m²</f>
+        <v/>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>713</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7010,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>HSV7.002a</t>
+          <t>HSV7.002b</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -7027,7 +7030,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek EPS 70F grey λ=0.032 tl. 160 mm — ETICS kontaktní zateplení fasády</t>
+          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -7039,12 +7042,12 @@
         <v>276.7</v>
       </c>
       <c r="I109" s="3">
-        <f> HSV7.002 plocha fasády 276.7 m²</f>
+        <f> HSV7.002 plocha 276.7 m²</f>
         <v/>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -7069,7 +7072,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>HSV7.002b</t>
+          <t>HSV7.003a</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -7089,7 +7092,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -7098,20 +7101,20 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="I110" s="3">
-        <f> HSV7.002 plocha 276.7 m²</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -7121,7 +7124,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7134,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>HSV7.003a</t>
+          <t>HSV7.003b</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7151,7 +7154,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -7168,7 +7171,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>781</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
@@ -7193,7 +7196,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>HSV7.003b</t>
+          <t>HSV7.004a</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -7213,29 +7216,29 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="I112" s="3">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
         <v/>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -7245,7 +7248,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7258,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>HSV7.004a</t>
+          <t>HSV7.004b</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -7275,7 +7278,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -7287,7 +7290,7 @@
         <v>82.2</v>
       </c>
       <c r="I113" s="3">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -7317,7 +7320,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>HSV7.004b</t>
+          <t>HSV7.005</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7337,34 +7340,35 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="I114" s="3">
-        <f> HSV7.004 obvod 82.2 bm</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -7379,7 +7383,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>HSV7.005</t>
+          <t>HSV7.006</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7399,40 +7403,40 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>1</v>
+        <v>290.2</v>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
+          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01, S12a, S12b</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7446,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>HSV7.006</t>
+          <t>PSV71.001</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -7452,17 +7456,17 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -7471,21 +7475,21 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -7493,11 +7497,7 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>PSV71.001</t>
+          <t>PSV71.002</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -7525,30 +7525,30 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
+          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>PSV71.002</t>
+          <t>PSV71.003</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7584,30 +7584,26 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>712381111</t>
-        </is>
-      </c>
+          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -7623,7 +7619,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>PSV71.003</t>
+          <t>PSV71.101</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -7633,17 +7629,17 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -7652,17 +7648,17 @@
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
+          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -7678,7 +7674,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PSV71.101</t>
+          <t>PSV71.102</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7698,7 +7694,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -7707,17 +7703,16 @@
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="I120" s="3">
+        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
+        <v/>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -7725,7 +7720,11 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -7733,7 +7732,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>PSV71.102</t>
+          <t>PSV76.001</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7743,35 +7742,40 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="I121" s="3">
-        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
-        <v/>
-      </c>
-      <c r="J121" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>766621011</t>
+        </is>
+      </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -7779,11 +7783,7 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PSV76.001</t>
+          <t>PSV76.002</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -7820,11 +7820,11 @@
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>PSV76.002</t>
+          <t>PSV76.003</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -7879,11 +7879,11 @@
         </is>
       </c>
       <c r="H123" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>PSV76.003</t>
+          <t>PSV76.004</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -7938,11 +7938,11 @@
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PSV76.004</t>
+          <t>PSV76.005</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -7997,11 +7997,11 @@
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>PSV76.005</t>
+          <t>PSV76.006</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>PSV76.006</t>
+          <t>PSV76.007</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -8115,11 +8115,11 @@
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>PSV76.007</t>
+          <t>PSV76.008</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>PSV76.008</t>
+          <t>PSV76.009</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="H129" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+          <t>TZ ARS — vstupní plastové dveře</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>PSV76.009</t>
+          <t>PSV76.010</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -8292,21 +8292,21 @@
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — vstupní plastové dveře</t>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>PSV76.010</t>
+          <t>PSV76.101</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -8332,45 +8332,45 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H131" s="2" t="n">
-        <v>15</v>
+        <v>69.5</v>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
+          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr"/>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>PSV76.101</t>
+          <t>PSV76.102</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -8410,21 +8410,20 @@
         </is>
       </c>
       <c r="H132" s="2" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
-        </is>
+        <v>20.8</v>
+      </c>
+      <c r="I132" s="3">
+        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
+        <v/>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -8440,7 +8439,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>PSV76.102</t>
+          <t>PSV76.103a</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -8460,7 +8459,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn Ø100 mm — 4 svody</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -8469,25 +8468,26 @@
         </is>
       </c>
       <c r="H133" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I133" s="3">
-        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
-        <v/>
+        <v>28</v>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>4 svody × ~7 m výška = 28 bm</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>PSV76.103a</t>
+          <t>PSV76.103b</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn Ø100 mm — 4 svody</t>
+          <t>Podokapní žlaby Pzn — po obvodu střechy</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -8527,12 +8527,11 @@
         </is>
       </c>
       <c r="H134" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>4 svody × ~7 m výška = 28 bm</t>
-        </is>
+        <v>15.5</v>
+      </c>
+      <c r="I134" s="3">
+        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
+        <v/>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -8557,7 +8556,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>PSV76.103b</t>
+          <t>PSV76.104</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8577,7 +8576,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Podokapní žlaby Pzn — po obvodu střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -8586,25 +8585,26 @@
         </is>
       </c>
       <c r="H135" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I135" s="3">
-        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
-        <v/>
+        <v>26.1</v>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
+        </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>PSV76.104</t>
+          <t>PSV76.201</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -8625,45 +8625,45 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H136" s="2" t="n">
-        <v>26.1</v>
+        <v>1</v>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>PSV76.201</t>
+          <t>PSV76.202</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>PSV76.202</t>
+          <t>PSV76.203</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -8753,35 +8753,35 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>1 schodiště do podkroví (TZ ARS)</t>
+          <t>2 vstupy</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr"/>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>PSV76.203</t>
+          <t>PSV76.204</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -8812,30 +8812,30 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>2 vstupy</t>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>PSV76.204</t>
+          <t>PSV76.301</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8861,40 +8861,40 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+          <t>2 schodiště × ~8 stupňů = 16</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>PSV76.301</t>
+          <t>PSV76.302a</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -8930,35 +8930,34 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>2 schodiště × ~8 stupňů = 16</t>
-        </is>
+        <v>9.23</v>
+      </c>
+      <c r="I141" s="3">
+        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
+        <v/>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>762</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr"/>
@@ -8969,7 +8968,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>PSV76.302a</t>
+          <t>PSV76.302b</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8989,7 +8988,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
+          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9027,7 +9026,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>PSV76.302b</t>
+          <t>PSV77.001</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -9037,17 +9036,17 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -9056,25 +9055,26 @@
         </is>
       </c>
       <c r="H143" s="2" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="I143" s="3">
-        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
-        <v/>
+        <v>171.5</v>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr"/>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>PSV77.001</t>
+          <t>PSV77.002a</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9114,26 +9114,25 @@
         </is>
       </c>
       <c r="H144" s="2" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
-        </is>
+        <v>13.5</v>
+      </c>
+      <c r="I144" s="3">
+        <f> PSV77.002 plocha 13.5 m²</f>
+        <v/>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr"/>
@@ -9144,7 +9143,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>PSV77.002a</t>
+          <t>PSV77.002b</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -9164,7 +9163,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
+          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -9202,7 +9201,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>PSV77.002b</t>
+          <t>PSV77.003a</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -9222,7 +9221,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
+          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -9231,10 +9230,10 @@
         </is>
       </c>
       <c r="H146" s="2" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="I146" s="3">
-        <f> PSV77.002 plocha 13.5 m²</f>
+        <f> PSV77.003 plocha 32.4 m²</f>
         <v/>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -9244,7 +9243,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -9260,7 +9259,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>PSV77.003a</t>
+          <t>PSV77.003b</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -9280,7 +9279,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
+          <t>Spárování keramické dlažby + úklid — 1.PP</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -9318,7 +9317,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>PSV77.003b</t>
+          <t>PSV77.004</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -9338,7 +9337,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9347,25 +9346,26 @@
         </is>
       </c>
       <c r="H148" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I148" s="3">
-        <f> PSV77.003 plocha 32.4 m²</f>
-        <v/>
+        <v>25</v>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
+        </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr"/>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>PSV77.004</t>
+          <t>PSV77.005</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -9405,21 +9405,21 @@
         </is>
       </c>
       <c r="H149" s="2" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>PSV77.005</t>
+          <t>PSV77.006</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -9455,30 +9455,30 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H150" s="2" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>PSV77.006</t>
+          <t>PSV77.007</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -9523,21 +9523,21 @@
         </is>
       </c>
       <c r="H151" s="2" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>PSV77.007</t>
+          <t>PSV78.001a</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -9563,45 +9563,44 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
-        </is>
+        <v>78.2</v>
+      </c>
+      <c r="I152" s="3">
+        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
+        <v/>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr"/>
@@ -9612,7 +9611,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>PSV78.001a</t>
+          <t>PSV78.001b</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -9632,7 +9631,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
+          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -9644,7 +9643,7 @@
         <v>78.2</v>
       </c>
       <c r="I153" s="3">
-        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
+        <f> PSV78.001 plocha 78.2 m²</f>
         <v/>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -9670,7 +9669,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>PSV78.001b</t>
+          <t>PSV78.002a</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -9690,7 +9689,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -9699,10 +9698,10 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="I154" s="3">
-        <f> PSV78.001 plocha 78.2 m²</f>
+        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
         <v/>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -9712,7 +9711,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -9728,7 +9727,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>PSV78.002a</t>
+          <t>PSV78.002b</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -9748,7 +9747,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -9760,7 +9759,7 @@
         <v>208.4</v>
       </c>
       <c r="I155" s="3">
-        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
+        <f> PSV78.002 plocha 208.4 m²</f>
         <v/>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -9786,7 +9785,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>PSV78.002b</t>
+          <t>PSV78.003a</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -9806,7 +9805,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -9815,10 +9814,10 @@
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="I156" s="3">
-        <f> PSV78.002 plocha 208.4 m²</f>
+        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
         <v/>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -9828,7 +9827,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -9844,7 +9843,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>PSV78.003a</t>
+          <t>PSV78.003b</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -9864,7 +9863,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -9876,7 +9875,7 @@
         <v>201.6</v>
       </c>
       <c r="I157" s="3">
-        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
+        <f> PSV78.003 plocha 201.6 m²</f>
         <v/>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -9902,7 +9901,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>PSV78.003b</t>
+          <t>PSV78.004a</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -9922,7 +9921,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -9931,10 +9930,10 @@
         </is>
       </c>
       <c r="H158" s="2" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="I158" s="3">
-        <f> PSV78.003 plocha 201.6 m²</f>
+        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
         <v/>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -9944,7 +9943,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -9960,7 +9959,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>PSV78.004a</t>
+          <t>PSV78.004b</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -9980,7 +9979,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -9992,7 +9991,7 @@
         <v>179.1</v>
       </c>
       <c r="I159" s="3">
-        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <f> PSV78.004 plocha 179.1 m²</f>
         <v/>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -10018,7 +10017,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>PSV78.004b</t>
+          <t>PSV78.005</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -10038,7 +10037,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -10047,25 +10046,26 @@
         </is>
       </c>
       <c r="H160" s="2" t="n">
-        <v>179.1</v>
-      </c>
-      <c r="I160" s="3">
-        <f> PSV78.004 plocha 179.1 m²</f>
-        <v/>
+        <v>59.5</v>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
+        </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>PSV78.005</t>
+          <t>PSV78.006</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10105,11 +10105,11 @@
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>PSV78.006</t>
+          <t>PSV78.007</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -10164,11 +10164,11 @@
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>PSV78.007</t>
+          <t>PSV78.008</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -10223,21 +10223,21 @@
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>PSV78.008</t>
+          <t>PSV78.009</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -10282,11 +10282,11 @@
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>PSV78.009</t>
+          <t>PSV78.010</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -10341,11 +10341,11 @@
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>PSV78.010</t>
+          <t>PSV78.011</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -10400,11 +10400,11 @@
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>PSV78.011</t>
+          <t>PSV78.012</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -10459,21 +10459,21 @@
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012</t>
+          <t>PSV95.001</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -10499,45 +10499,45 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr"/>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>PSV95.001</t>
+          <t>PSV95.002</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -10577,26 +10577,26 @@
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr"/>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>PSV95.002</t>
+          <t>PSV76.001</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -10640,17 +10640,17 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ — min. 1 ks 34A</t>
+          <t>1 ks vstupní dveře skladu</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>PSV76.001</t>
+          <t>PSV77.001</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -10676,48 +10676,48 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
-        <v>1</v>
+        <v>17.6</v>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>766682111</t>
-        </is>
-      </c>
+          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr"/>
+          <t>wrong_leaf_disambiguation_needed</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -10725,58 +10725,58 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>PSV77.001</t>
+          <t>PSV72.001</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>17.6</v>
+        <v>1</v>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>722290515</t>
+        </is>
+      </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
-        </is>
-      </c>
-      <c r="M172" s="2" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
+          <t>FAMILY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>PSV72.001</t>
+          <t>PSV72.002</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -10804,30 +10804,30 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
+          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>PSV72.002</t>
+          <t>PSV72.003</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -10872,26 +10872,26 @@
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
+          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr"/>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>PSV72.003</t>
+          <t>PSV72.004a</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -10922,35 +10922,35 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Vana — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
+          <t>1× vana (DXF sanit_vana)</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr"/>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004a</t>
+          <t>PSV72.004b</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Vana — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>1× vana (DXF sanit_vana)</t>
+          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004b</t>
+          <t>PSV72.004c</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
+          <t>1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004c</t>
+          <t>PSV72.005a</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>1× WC (TZ standard)</t>
+          <t>1× umyvadlo (DXF)</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005a</t>
+          <t>PSV72.005b</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (DXF)</t>
+          <t>1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005b</t>
+          <t>PSV72.005c</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>1× WC (TZ standard)</t>
+          <t>1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005c</t>
+          <t>PSV72.006a</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>1× sprcha (TZ standard)</t>
+          <t>1× WC (DXF)</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006a</t>
+          <t>PSV72.006b</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>1× WC (DXF)</t>
+          <t>1× umyvadlo (TZ standard)</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006b</t>
+          <t>PSV72.006c</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (TZ standard)</t>
+          <t>1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006c</t>
+          <t>PSV72.007</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -11462,26 +11462,26 @@
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>1× sprcha (TZ standard)</t>
+          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>PSV72.007</t>
+          <t>PSV72.008a</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Rohový ventil WC — dodávka + montáž</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -11521,26 +11521,26 @@
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
+          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr"/>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008a</t>
+          <t>PSV72.008b</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Rohový ventil WC — dodávka + montáž</t>
+          <t>Páková umyvadlová baterie — dodávka + montáž</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
+          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008b</t>
+          <t>PSV72.008c</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Páková umyvadlová baterie — dodávka + montáž</t>
+          <t>Sprchová / vanová baterie termostatická — dodávka + montáž</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
+          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008c</t>
+          <t>PSV72.008d</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Sprchová / vanová baterie termostatická — dodávka + montáž</t>
+          <t>Dřezová baterie kuchyňská — dodávka + montáž</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -11698,11 +11698,11 @@
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
+          <t>2× kuchyně (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008d</t>
+          <t>PSV72.009</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Dřezová baterie kuchyňská — dodávka + montáž</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -11757,26 +11757,26 @@
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>2× kuchyně (1.06 + 3.05)</t>
+          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>PSV72.009</t>
+          <t>PSV72.010</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -11820,17 +11820,17 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
+          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>PSV72.010</t>
+          <t>PSV73.001</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -11856,17 +11856,17 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -11879,17 +11879,17 @@
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
+          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>PSV73.001</t>
+          <t>PSV73.002</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -11925,30 +11925,29 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H192" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I192" s="3" t="inlineStr">
-        <is>
-          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
-        </is>
+      <c r="I192" s="3">
+        <f> ks kamen</f>
+        <v/>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -11964,7 +11963,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>PSV73.002</t>
+          <t>PSV73.003</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -11984,29 +11983,30 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I193" s="3">
-        <f> ks kamen</f>
-        <v/>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
+        </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>PSV73.003</t>
+          <t>PSV73.004</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -12055,17 +12055,17 @@
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
+          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>PSV73.004</t>
+          <t>PSV73.005</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -12114,17 +12114,17 @@
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
+          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>PSV73.005</t>
+          <t>PSV73.006</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -12169,21 +12169,21 @@
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
+          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>PSV73.006</t>
+          <t>PSV73.007</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -12219,30 +12219,30 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
+          <t>TZ ARS — komín revize a úpravy stávajícího</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="L197" s="2" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>PSV73.007</t>
+          <t>PSV73.008</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -12278,30 +12278,30 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — komín revize a úpravy stávajícího</t>
+          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>PSV73.008</t>
+          <t>M21.001</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -12327,40 +12327,40 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>M21.001</t>
+          <t>M21.002</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -12396,30 +12396,30 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>M21.002</t>
+          <t>M21.003</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -12455,30 +12455,30 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>4</v>
+        <v>700</v>
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>M21.003</t>
+          <t>M21.004</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -12514,30 +12514,30 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>M21.004</t>
+          <t>M21.005</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -12582,21 +12582,21 @@
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="L203" s="2" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>M21.005</t>
+          <t>M21.006</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -12632,30 +12632,30 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>M21.006</t>
+          <t>M21.007</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -12704,17 +12704,17 @@
       </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>M21.007</t>
+          <t>VRN.001</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -12740,40 +12740,40 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>VRN.001</t>
+          <t>VRN.002</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="H207" s="2" t="n">
@@ -12822,17 +12822,17 @@
       </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
+          <t>1 ks × 8 měs realizace</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>VRN.002</t>
+          <t>VRN.003</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -12868,30 +12868,30 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>1 ks × 8 měs realizace</t>
+          <t>Komplexní zřízení + provoz po dobu stavby</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>VRN.003</t>
+          <t>VRN.101</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -12917,40 +12917,40 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H209" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>Komplexní zřízení + provoz po dobu stavby</t>
+          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>VRN.101</t>
+          <t>VRN.201</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -12976,40 +12976,40 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
+          <t>realizace ~8 měs</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>VRN.201</t>
+          <t>VRN.301</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -13035,22 +13035,22 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
@@ -13058,17 +13058,17 @@
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>realizace ~8 měs</t>
+          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>VRN.301</t>
+          <t>VRN.302</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -13104,12 +13104,12 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
@@ -13117,17 +13117,17 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
+          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>VRN.302</t>
+          <t>VRN.401</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -13153,17 +13153,17 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -13176,17 +13176,17 @@
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
+          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="L213" s="2" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>VRN.401</t>
+          <t>VRN.402</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -13235,17 +13235,17 @@
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
+          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>VRN.402</t>
+          <t>VRN.501</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -13271,17 +13271,17 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -13290,21 +13290,21 @@
         </is>
       </c>
       <c r="H215" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
+          <t>2 etapy geodet × 1 kpl</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="L215" s="2" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>VRN.501</t>
+          <t>VRN.601</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -13330,17 +13330,17 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -13349,21 +13349,21 @@
         </is>
       </c>
       <c r="H216" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>2 etapy geodet × 1 kpl</t>
+          <t>Standard — DSP pro kolaudaci</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>VRN.601</t>
+          <t>VRN.701</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -13412,17 +13412,17 @@
       </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
-          <t>Standard — DSP pro kolaudaci</t>
+          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="L217" s="2" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>VRN.701</t>
+          <t>VRN.801</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -13448,22 +13448,22 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
@@ -13471,17 +13471,17 @@
       </c>
       <c r="I218" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
+          <t>Standard — paušál kolaudace</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>VRN.801</t>
+          <t>VRN.102</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -13507,17 +13507,17 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -13530,17 +13530,17 @@
       </c>
       <c r="I219" s="3" t="inlineStr">
         <is>
-          <t>Standard — paušál kolaudace</t>
+          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>VRN.102</t>
+          <t>VRN.103</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -13576,30 +13576,30 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>1</v>
+        <v>56.9</v>
       </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
+          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>VRN.103</t>
+          <t>VRN.001</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -13635,30 +13635,30 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>56.9</v>
+        <v>1</v>
       </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
+          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="L221" s="2" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>VRN.001</t>
+          <t>VRN.002</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -13694,30 +13694,30 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>VRN.002</t>
+          <t>VRN.101</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -13743,40 +13743,40 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
+          <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="L223" s="2" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>VRN.101</t>
+          <t>VRN.201</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -13802,22 +13802,22 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Společné</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Společné</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
@@ -13825,17 +13825,17 @@
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030001000</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
         </is>
       </c>
       <c r="L224" s="2" t="inlineStr">
@@ -13851,55 +13851,55 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>VRN.201</t>
+          <t>HSV6.013</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>carried_verified</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>HSV6.013</t>
+          <t>HSV6.014</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -13939,11 +13939,11 @@
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>HSV6.014</t>
+          <t>HSV6.015</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -13998,26 +13998,26 @@
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I227" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr"/>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>HSV6.015</t>
+          <t>PSV76.013</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -14038,17 +14038,17 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -14057,21 +14057,21 @@
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>PSV76.013</t>
+          <t>VRN.020</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -14097,22 +14097,22 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
@@ -14120,17 +14120,17 @@
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="L229" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>VRN.020</t>
+          <t>PSV76.014</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -14156,40 +14156,40 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="L230" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>PSV76.014</t>
+          <t>PSV72.004.A</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -14215,17 +14215,17 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -14234,21 +14234,21 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I231" s="3" t="inlineStr">
         <is>
-          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L231" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.A</t>
+          <t>PSV72.004.B</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.B</t>
+          <t>PSV72.004.C</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.C</t>
+          <t>PSV72.005.A</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -14415,17 +14415,17 @@
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L234" s="2" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.A</t>
+          <t>PSV72.005.B</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.B</t>
+          <t>PSV72.005.C</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.C</t>
+          <t>PSV72.006.A</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L237" s="2" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.A</t>
+          <t>PSV72.006.B</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.B</t>
+          <t>PSV72.006.C</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.C</t>
+          <t>PSV78.012.1_PP</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -14746,40 +14746,40 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>1</v>
+        <v>78.2</v>
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.1_PP</t>
+          <t>PSV78.012.1_NP</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -14824,11 +14824,11 @@
         </is>
       </c>
       <c r="H241" s="2" t="n">
-        <v>78.2</v>
+        <v>254.5</v>
       </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
-          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="L241" s="2" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.1_NP</t>
+          <t>PSV78.012.2_NP</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -14883,11 +14883,11 @@
         </is>
       </c>
       <c r="H242" s="2" t="n">
-        <v>254.5</v>
+        <v>247.5</v>
       </c>
       <c r="I242" s="3" t="inlineStr">
         <is>
-          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="L242" s="2" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.2_NP</t>
+          <t>PSV78.012.3_NP</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -14942,11 +14942,11 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="I243" s="3" t="inlineStr">
         <is>
-          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="L243" s="2" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.3_NP</t>
+          <t>HSV6.016</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -14982,45 +14982,45 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H244" s="2" t="n">
-        <v>219.3</v>
+        <v>0.6</v>
       </c>
       <c r="I244" s="3" t="inlineStr">
         <is>
-          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr"/>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>HSV6.016</t>
+          <t>HSV6.017</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -15060,21 +15060,21 @@
         </is>
       </c>
       <c r="H245" s="2" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>HSV6.017</t>
+          <t>HSV1.015a</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -15100,45 +15100,44 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="I246" s="3">
+        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <v/>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>212</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr"/>
@@ -15149,7 +15148,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015a</t>
+          <t>HSV1.015b</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -15169,7 +15168,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
+          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -15181,7 +15180,7 @@
         <v>12</v>
       </c>
       <c r="I247" s="3">
-        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <f> HSV1.015 délka drenáže 12 m</f>
         <v/>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -15207,7 +15206,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015b</t>
+          <t>HSV1.015c</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -15227,7 +15226,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
+          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -15239,12 +15238,12 @@
         <v>12</v>
       </c>
       <c r="I248" s="3">
-        <f> HSV1.015 délka drenáže 12 m</f>
+        <f> HSV1.015 délka 12 m</f>
         <v/>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>693</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -15265,57 +15264,62 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015c</t>
+          <t>HSV5.001</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H249" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I249" s="3">
-        <f> HSV1.015 délka 12 m</f>
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="I249" s="3" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
+        </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
-        </is>
-      </c>
-      <c r="M249" s="2" t="inlineStr"/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -15323,50 +15327,46 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>HSV5.001</t>
+          <t>VRN.PM01</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I250" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="J250" s="2" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
+          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -15374,11 +15374,7 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M250" s="2" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="M250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -15386,7 +15382,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>VRN.PM01</t>
+          <t>VRN.PM02</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -15396,36 +15392,36 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>0</v>
+        <v>503.1</v>
       </c>
       <c r="I251" s="3" t="inlineStr">
         <is>
-          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
+          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
@@ -15441,7 +15437,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>VRN.PM02</t>
+          <t>HSV1.016</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -15451,44 +15447,48 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>503.1</v>
+        <v>13</v>
       </c>
       <c r="I252" s="3" t="inlineStr">
         <is>
-          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
+          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Situace měření 2026-05-29 (rameno 8×175×280 + rameno 5×175×280) + TZ statika §3.2.5 'schody na terénu z betonových dílců do betonového lože'</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M252" s="2" t="inlineStr"/>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>Venkovní schody na terénu</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>HSV1.016</t>
+          <t>HSV5.017a</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -15506,17 +15506,17 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -15525,27 +15525,30 @@
         </is>
       </c>
       <c r="H253" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I253" s="3" t="inlineStr">
-        <is>
-          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
-        </is>
-      </c>
-      <c r="J253" s="2" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="I253" s="3">
+        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
+        <v/>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>762085112</t>
+        </is>
+      </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>Situace měření 2026-05-29 (rameno 8×175×280 + rameno 5×175×280) + TZ statika §3.2.5 'schody na terénu z betonových dílců do betonového lože'</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>carried_verified</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu</t>
+          <t>Krov — spojovací prostředky</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15558,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017a</t>
+          <t>HSV5.017b</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -15575,24 +15578,24 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
+          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="I254" s="3">
-        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
+        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
         <v/>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>762085112</t>
+          <t>31197004</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -15602,7 +15605,7 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
@@ -15617,7 +15620,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017b</t>
+          <t>HSV5.017c</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -15637,24 +15640,24 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
+          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>100 ks</t>
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I255" s="3">
-        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
+        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
         <v/>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>31197004</t>
+          <t>3111006</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -15679,7 +15682,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017c</t>
+          <t>HSV5.017d</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -15699,7 +15702,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
+          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -15716,7 +15719,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>3111006</t>
+          <t>31121004</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -15741,7 +15744,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017d</t>
+          <t>HSV4.015a</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -15751,39 +15754,39 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
+          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>100 ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H257" s="2" t="n">
-        <v>1</v>
+        <v>59.5</v>
       </c>
       <c r="I257" s="3">
-        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
+        <f> plocha stropu S07</f>
         <v/>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>31121004</t>
+          <t>713191</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
+          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
         </is>
       </c>
       <c r="L257" s="2" t="inlineStr">
@@ -15793,7 +15796,7 @@
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>Krov — spojovací prostředky</t>
+          <t>S07</t>
         </is>
       </c>
     </row>
@@ -15803,7 +15806,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>HSV4.015a</t>
+          <t>HSV4.015b</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15823,7 +15826,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
+          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -15832,17 +15835,13 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>59.5</v>
+        <v>62.5</v>
       </c>
       <c r="I258" s="3">
-        <f> plocha stropu S07</f>
+        <f> 59.5 × 1.05 prořez</f>
         <v/>
       </c>
-      <c r="J258" s="2" t="inlineStr">
-        <is>
-          <t>713191</t>
-        </is>
-      </c>
+      <c r="J258" s="2" t="inlineStr"/>
       <c r="K258" s="3" t="inlineStr">
         <is>
           <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
@@ -15850,7 +15849,7 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
@@ -15865,7 +15864,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>HSV4.015b</t>
+          <t>HSV4.016a</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -15885,7 +15884,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
+          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -15894,16 +15893,16 @@
         </is>
       </c>
       <c r="H259" s="2" t="n">
-        <v>62.5</v>
+        <v>65.5</v>
       </c>
       <c r="I259" s="3">
-        <f> 59.5 × 1.05 prořez</f>
+        <f> 59.5 × 1.10 přesahy</f>
         <v/>
       </c>
       <c r="J259" s="2" t="inlineStr"/>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
+          <t>skladba S07 návrh — separační geotextilie</t>
         </is>
       </c>
       <c r="L259" s="2" t="inlineStr">
@@ -15923,7 +15922,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>HSV4.016a</t>
+          <t>HSV4.017a</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -15943,7 +15942,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
+          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -15952,26 +15951,30 @@
         </is>
       </c>
       <c r="H260" s="2" t="n">
-        <v>65.5</v>
+        <v>104.4</v>
       </c>
       <c r="I260" s="3">
-        <f> 59.5 × 1.10 přesahy</f>
+        <f> plocha stropu S09</f>
         <v/>
       </c>
-      <c r="J260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>713121</t>
+        </is>
+      </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — separační geotextilie</t>
+          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S09</t>
         </is>
       </c>
     </row>
@@ -15981,7 +15984,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>HSV4.017a</t>
+          <t>HSV4.017b</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -16001,7 +16004,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
+          <t>Minerální vata 180/200 mm — materiál</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -16010,17 +16013,13 @@
         </is>
       </c>
       <c r="H261" s="2" t="n">
-        <v>104.4</v>
+        <v>109.6</v>
       </c>
       <c r="I261" s="3">
-        <f> plocha stropu S09</f>
+        <f> 104.4 × 1.05</f>
         <v/>
       </c>
-      <c r="J261" s="2" t="inlineStr">
-        <is>
-          <t>713121</t>
-        </is>
-      </c>
+      <c r="J261" s="2" t="inlineStr"/>
       <c r="K261" s="3" t="inlineStr">
         <is>
           <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
@@ -16028,7 +16027,7 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
@@ -16043,7 +16042,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>HSV4.017b</t>
+          <t>HSV4.018a</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -16063,7 +16062,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Minerální vata 180/200 mm — materiál</t>
+          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -16071,17 +16070,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H262" s="2" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="I262" s="3">
-        <f> 104.4 × 1.05</f>
-        <v/>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
       </c>
       <c r="J262" s="2" t="inlineStr"/>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
+          <t>skladba S08 legenda (řez nepretíná, plocha nepřiřazena)</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
@@ -16091,7 +16093,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S08</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16103,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>HSV4.018a</t>
+          <t>HSV4.019a</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -16121,7 +16123,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
+          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -16139,10 +16141,14 @@
           <t>neurčeno — V1</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr"/>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>713191</t>
+        </is>
+      </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda (řez nepretíná, plocha nepřiřazena)</t>
+          <t>skladba S08 legenda</t>
         </is>
       </c>
       <c r="L263" s="2" t="inlineStr">
@@ -16162,7 +16168,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>HSV4.019a</t>
+          <t>HSV4.020a</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -16182,7 +16188,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
+          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -16200,11 +16206,7 @@
           <t>neurčeno — V1</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr">
-        <is>
-          <t>713191</t>
-        </is>
-      </c>
+      <c r="J264" s="2" t="inlineStr"/>
       <c r="K264" s="3" t="inlineStr">
         <is>
           <t>skladba S08 legenda</t>
@@ -16227,7 +16229,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>HSV4.020a</t>
+          <t>HSV4.021a</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -16247,7 +16249,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
+          <t>Separační vrstva — S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -16288,7 +16290,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>HSV4.021a</t>
+          <t>HSV7.007a</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -16298,17 +16300,17 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Separační vrstva — S08 (neurčeno)</t>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -16316,20 +16318,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H266" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I266" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — V1</t>
-        </is>
+      <c r="H266" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I266" s="3">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -16339,7 +16338,7 @@
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
@@ -16349,7 +16348,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>HSV7.007a</t>
+          <t>HSV7.007b</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16369,7 +16368,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -16378,10 +16377,10 @@
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I267" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
@@ -16407,7 +16406,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>HSV7.007b</t>
+          <t>HSV7.008a</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -16427,7 +16426,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -16436,16 +16435,16 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I268" s="3">
-        <f> 23 × 1.05</f>
+        <f> 23 × 1.10</f>
         <v/>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>Řez A-A/C-C sokl + obvod ETICS</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -16465,7 +16464,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>HSV7.008a</t>
+          <t>HSV7.009a</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -16485,7 +16484,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -16494,16 +16493,16 @@
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I269" s="3">
-        <f> 23 × 1.10</f>
+        <f> 23 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A/C-C sokl + obvod ETICS</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="L269" s="2" t="inlineStr">
@@ -16523,7 +16522,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>HSV7.009a</t>
+          <t>HSV7.009b</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -16543,7 +16542,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
+          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -16552,13 +16551,17 @@
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I270" s="3">
-        <f> 23 (OVĚŘIT)</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
-      <c r="J270" s="2" t="inlineStr"/>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
           <t>Řez A-A sokl tags S03b + obvod ETICS</t>
@@ -16566,7 +16569,7 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M270" s="2" t="inlineStr">
@@ -16581,7 +16584,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>HSV7.009b</t>
+          <t>HSV5.018a</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -16591,17 +16594,17 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
+          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -16610,30 +16613,26 @@
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="I271" s="3">
-        <f> 23 × 1.05</f>
+        <f> 140.94 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="J271" s="2" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
+      <c r="J271" s="2" t="inlineStr"/>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>skladba S10 návrh — pojistná HI pod Al krytinu</t>
         </is>
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S10</t>
         </is>
       </c>
     </row>
@@ -16643,7 +16642,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>HSV5.018a</t>
+          <t>HSV6.018a</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -16653,17 +16652,17 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -16672,16 +16671,16 @@
         </is>
       </c>
       <c r="H272" s="2" t="n">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="I272" s="3">
-        <f> 140.94 × 1.10 přesahy</f>
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>skladba S10 návrh — pojistná HI pod Al krytinu</t>
+          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
         </is>
       </c>
       <c r="L272" s="2" t="inlineStr">
@@ -16691,7 +16690,7 @@
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
@@ -16701,27 +16700,27 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>HSV6.018a</t>
+          <t>HSV5.002a</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV 5 Komunikace pozemní — dlažby</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
+          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -16729,17 +16728,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H273" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I273" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
-        <v/>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
+        </is>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
       <c r="K273" s="3" t="inlineStr">
         <is>
-          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="L273" s="2" t="inlineStr">
@@ -16747,11 +16749,7 @@
           <t>needs_lookup</t>
         </is>
       </c>
-      <c r="M273" s="2" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
+      <c r="M273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -16759,7 +16757,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002a</t>
+          <t>HSV5.002b</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -16779,7 +16777,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -16794,7 +16792,7 @@
       </c>
       <c r="I274" s="3" t="inlineStr">
         <is>
-          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
+          <t>neurčeno — OVĚŘIT</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
@@ -16816,7 +16814,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002b</t>
+          <t>HSV5.002c</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -16836,12 +16834,12 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -16873,7 +16871,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002c</t>
+          <t>PSV76.002a</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -16883,38 +16881,35 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>HSV 5 Komunikace pozemní — dlažby</t>
+          <t>PSV 767 zámečnické konstrukce</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+          <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="H276" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" s="3">
+        <f> 1 brána</f>
+        <v/>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="L276" s="2" t="inlineStr">
@@ -16930,7 +16925,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>PSV76.002a</t>
+          <t>VRN.003a</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -16940,35 +16935,35 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>PSV 767 zámečnické konstrukce</t>
+          <t>VRN geodetické + zaměřovací práce</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Vjezdová brána ocelová — dodávka + montáž</t>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H277" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I277" s="3">
-        <f> 1 brána</f>
+        <f> 1 soubor</f>
         <v/>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
       <c r="K277" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
         </is>
       </c>
       <c r="L277" s="2" t="inlineStr">
@@ -16984,45 +16979,45 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>VRN.003a</t>
+          <t>M24.001a</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>VRN geodetické + zaměřovací práce</t>
+          <t>M / 751 vzduchotechnika — odtah digestoře</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
+          <t>Lokální odtah digestoře kuchyně + prostup + zpětná klapka</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I278" s="3">
-        <f> 1 soubor</f>
+        <f> 2 kuchyně (1.NP + 3.NP)</f>
         <v/>
       </c>
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr">
@@ -17038,7 +17033,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>M24.001a</t>
+          <t>M21.008a</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -17048,35 +17043,35 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>M-24 VZT</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>M / 751 vzduchotechnika — odtah digestoře</t>
+          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Lokální odtah digestoře kuchyně + prostup + zpětná klapka</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H279" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I279" s="3">
-        <f> 2 kuchyně (1.NP + 3.NP)</f>
+        <f> 1 soubor</f>
         <v/>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
       <c r="K279" s="3" t="inlineStr">
         <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="L279" s="2" t="inlineStr">
@@ -17092,7 +17087,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>M21.008a</t>
+          <t>M21.008b</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -17112,7 +17107,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
+          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -17146,7 +17141,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>M21.008b</t>
+          <t>PSV95.003a</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -17156,17 +17151,17 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
+          <t>VRN doklady / revize požární</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -17184,7 +17179,7 @@
       <c r="J281" s="2" t="inlineStr"/>
       <c r="K281" s="3" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="L281" s="2" t="inlineStr">
@@ -17194,62 +17189,8 @@
       </c>
       <c r="M281" s="2" t="inlineStr"/>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
-        <v>281</v>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>PSV95.003a</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>PSV-95 Detekce požární</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="inlineStr">
-        <is>
-          <t>VRN doklady / revize požární</t>
-        </is>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="H282" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I282" s="3">
-        <f> 1 soubor</f>
-        <v/>
-      </c>
-      <c r="J282" s="2" t="inlineStr"/>
-      <c r="K282" s="3" t="inlineStr">
-        <is>
-          <t>PBŘ D.3</t>
-        </is>
-      </c>
-      <c r="L282" s="2" t="inlineStr">
-        <is>
-          <t>needs_lookup</t>
-        </is>
-      </c>
-      <c r="M282" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M282"/>
+  <autoFilter ref="A1:M281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Armovací vrstva — výztužná síťka + lepicí stěrka (zatírací) na ETICS</t>
+          <t>Armovací vrstva ETICS — lepicí/stěrková hmota (zatírací) + vmáčknutí tkaniny</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>HSV7.003a</t>
+          <t>HSV7.002c</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Výztužná síťka — sklovláknité pletivo vtlačené do tmelu, stěn (ETICS)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -7101,30 +7101,30 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="I110" s="3">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.002 plocha 276.7 m² (přesahy v spotřebě)</f>
         <v/>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622142001</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>leaf_verified</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>HSV7.003b</t>
+          <t>HSV7.003a</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>713</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>HSV7.004a</t>
+          <t>HSV7.003b</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -7216,29 +7216,29 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="I112" s="3">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
+        <f> HSV7.003 plocha soklu 13.5 m²</f>
         <v/>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>781</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>HSV7.004b</t>
+          <t>HSV7.004a</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
         <v>82.2</v>
       </c>
       <c r="I113" s="3">
-        <f> HSV7.004 obvod 82.2 bm</f>
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
         <v/>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>HSV7.005</t>
+          <t>HSV7.004b</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7340,35 +7340,34 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I114" s="3" t="inlineStr">
-        <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
-        </is>
+        <v>82.2</v>
+      </c>
+      <c r="I114" s="3">
+        <f> HSV7.004 obvod 82.2 bm</f>
+        <v/>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -7383,7 +7382,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>HSV7.006</t>
+          <t>HSV7.005</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7403,40 +7402,40 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>290.2</v>
+        <v>1</v>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+          <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>S01, S12a, S12b</t>
+          <t>S01, S12a</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7445,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>PSV71.001</t>
+          <t>HSV7.006</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -7456,17 +7455,17 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -7475,21 +7474,21 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>290.2</v>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
+          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -7497,7 +7496,11 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7505,7 +7508,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>PSV71.002</t>
+          <t>PSV71.001</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -7525,30 +7528,30 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>12</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
+          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>712381111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -7564,7 +7567,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>PSV71.003</t>
+          <t>PSV71.002</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7584,26 +7587,30 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.5</v>
+        <v>12</v>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr"/>
+          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>712381111</t>
+        </is>
+      </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -7619,7 +7626,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>PSV71.101</t>
+          <t>PSV71.003</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -7629,17 +7636,17 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -7648,17 +7655,17 @@
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>177.5</v>
+        <v>40.5</v>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
+          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -7674,7 +7681,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PSV71.102</t>
+          <t>PSV71.101</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7694,7 +7701,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -7703,16 +7710,17 @@
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="I120" s="3">
-        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
-        <v/>
+        <v>177.5</v>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
+        </is>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -7720,11 +7728,7 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+      <c r="M120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -7732,7 +7736,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>PSV76.001</t>
+          <t>PSV71.102</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7742,40 +7746,35 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>766621011</t>
-        </is>
-      </c>
+        <v>104.4</v>
+      </c>
+      <c r="I121" s="3">
+        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
+        <v/>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -7783,7 +7782,11 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7791,7 +7794,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PSV76.002</t>
+          <t>PSV76.001</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7811,7 +7814,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -7820,11 +7823,11 @@
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -7834,12 +7837,12 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr"/>
@@ -7850,7 +7853,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>PSV76.003</t>
+          <t>PSV76.002</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7870,7 +7873,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -7879,11 +7882,11 @@
         </is>
       </c>
       <c r="H123" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -7893,7 +7896,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -7909,7 +7912,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>PSV76.004</t>
+          <t>PSV76.003</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7929,7 +7932,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -7938,11 +7941,11 @@
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -7952,7 +7955,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -7968,7 +7971,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PSV76.005</t>
+          <t>PSV76.004</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7988,7 +7991,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -7997,11 +8000,11 @@
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -8011,7 +8014,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -8027,7 +8030,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>PSV76.006</t>
+          <t>PSV76.005</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -8047,7 +8050,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -8060,7 +8063,7 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -8070,7 +8073,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -8086,7 +8089,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>PSV76.007</t>
+          <t>PSV76.006</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -8106,7 +8109,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -8115,11 +8118,11 @@
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -8129,7 +8132,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -8145,7 +8148,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>PSV76.008</t>
+          <t>PSV76.007</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -8165,7 +8168,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -8174,21 +8177,21 @@
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -8204,7 +8207,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>PSV76.009</t>
+          <t>PSV76.008</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -8224,7 +8227,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8233,21 +8236,21 @@
         </is>
       </c>
       <c r="H129" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — vstupní plastové dveře</t>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -8263,7 +8266,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>PSV76.010</t>
+          <t>PSV76.009</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -8283,7 +8286,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -8292,21 +8295,21 @@
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
+          <t>TZ ARS — vstupní plastové dveře</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -8322,7 +8325,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>PSV76.101</t>
+          <t>PSV76.010</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -8332,45 +8335,45 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H131" s="2" t="n">
-        <v>69.5</v>
+        <v>15</v>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr"/>
@@ -8381,7 +8384,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>PSV76.102</t>
+          <t>PSV76.101</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -8401,7 +8404,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -8410,20 +8413,21 @@
         </is>
       </c>
       <c r="H132" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I132" s="3">
-        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
-        <v/>
+        <v>69.5</v>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
+        </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -8439,7 +8443,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>PSV76.103a</t>
+          <t>PSV76.102</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -8459,7 +8463,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn Ø100 mm — 4 svody</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -8468,26 +8472,25 @@
         </is>
       </c>
       <c r="H133" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>4 svody × ~7 m výška = 28 bm</t>
-        </is>
+        <v>20.8</v>
+      </c>
+      <c r="I133" s="3">
+        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
+        <v/>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr"/>
@@ -8498,7 +8501,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>PSV76.103b</t>
+          <t>PSV76.103a</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -8518,7 +8521,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Podokapní žlaby Pzn — po obvodu střechy</t>
+          <t>Dešťové svody Pzn Ø100 mm — 4 svody</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -8527,11 +8530,12 @@
         </is>
       </c>
       <c r="H134" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I134" s="3">
-        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
-        <v/>
+        <v>28</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>4 svody × ~7 m výška = 28 bm</t>
+        </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -8556,7 +8560,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>PSV76.104</t>
+          <t>PSV76.103b</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8576,7 +8580,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Podokapní žlaby Pzn — po obvodu střechy</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -8585,26 +8589,25 @@
         </is>
       </c>
       <c r="H135" s="2" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
-        </is>
+        <v>15.5</v>
+      </c>
+      <c r="I135" s="3">
+        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
+        <v/>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>764</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr"/>
@@ -8615,7 +8618,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>PSV76.201</t>
+          <t>PSV76.104</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -8625,45 +8628,45 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H136" s="2" t="n">
-        <v>1</v>
+        <v>26.1</v>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
+          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr"/>
@@ -8674,7 +8677,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>PSV76.202</t>
+          <t>PSV76.201</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -8694,7 +8697,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -8707,7 +8710,7 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>1 schodiště do podkroví (TZ ARS)</t>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -8717,7 +8720,7 @@
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -8733,7 +8736,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>PSV76.203</t>
+          <t>PSV76.202</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -8753,35 +8756,35 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>2 vstupy</t>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr"/>
@@ -8792,7 +8795,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>PSV76.204</t>
+          <t>PSV76.203</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -8812,30 +8815,30 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+          <t>2 vstupy</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -8851,7 +8854,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>PSV76.301</t>
+          <t>PSV76.204</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8861,40 +8864,40 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>2 schodiště × ~8 stupňů = 16</t>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -8910,7 +8913,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>PSV76.302a</t>
+          <t>PSV76.301</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -8930,34 +8933,35 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="I141" s="3">
-        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
-        <v/>
+        <v>16</v>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>2 schodiště × ~8 stupňů = 16</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr"/>
@@ -8968,7 +8972,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>PSV76.302b</t>
+          <t>PSV76.302a</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8988,7 +8992,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
+          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9026,7 +9030,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>PSV77.001</t>
+          <t>PSV76.302b</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -9036,17 +9040,17 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -9055,26 +9059,25 @@
         </is>
       </c>
       <c r="H143" s="2" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
-        </is>
+        <v>9.23</v>
+      </c>
+      <c r="I143" s="3">
+        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
+        <v/>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>762</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr"/>
@@ -9085,7 +9088,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>PSV77.002a</t>
+          <t>PSV77.001</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -9105,7 +9108,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9114,25 +9117,26 @@
         </is>
       </c>
       <c r="H144" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I144" s="3">
-        <f> PSV77.002 plocha 13.5 m²</f>
-        <v/>
+        <v>171.5</v>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
+        </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr"/>
@@ -9143,7 +9147,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>PSV77.002b</t>
+          <t>PSV77.002a</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -9163,7 +9167,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
+          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -9201,7 +9205,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>PSV77.003a</t>
+          <t>PSV77.002b</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -9221,7 +9225,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
+          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -9230,10 +9234,10 @@
         </is>
       </c>
       <c r="H146" s="2" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="I146" s="3">
-        <f> PSV77.003 plocha 32.4 m²</f>
+        <f> PSV77.002 plocha 13.5 m²</f>
         <v/>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -9243,7 +9247,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -9259,7 +9263,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>PSV77.003b</t>
+          <t>PSV77.003a</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -9279,7 +9283,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -9317,7 +9321,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>PSV77.004</t>
+          <t>PSV77.003b</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -9337,7 +9341,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Spárování keramické dlažby + úklid — 1.PP</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9346,26 +9350,25 @@
         </is>
       </c>
       <c r="H148" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
-        </is>
+        <v>32.4</v>
+      </c>
+      <c r="I148" s="3">
+        <f> PSV77.003 plocha 32.4 m²</f>
+        <v/>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>771</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr"/>
@@ -9376,7 +9379,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>PSV77.005</t>
+          <t>PSV77.004</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -9396,7 +9399,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -9405,21 +9408,21 @@
         </is>
       </c>
       <c r="H149" s="2" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -9435,7 +9438,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>PSV77.006</t>
+          <t>PSV77.005</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -9455,30 +9458,30 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H150" s="2" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -9494,7 +9497,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>PSV77.007</t>
+          <t>PSV77.006</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -9514,7 +9517,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -9523,21 +9526,21 @@
         </is>
       </c>
       <c r="H151" s="2" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -9553,7 +9556,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>PSV78.001a</t>
+          <t>PSV77.007</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -9563,44 +9566,45 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="I152" s="3">
-        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
-        <v/>
+        <v>19.28</v>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+        </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr"/>
@@ -9611,7 +9615,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>PSV78.001b</t>
+          <t>PSV78.001a</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -9631,7 +9635,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -9643,7 +9647,7 @@
         <v>78.2</v>
       </c>
       <c r="I153" s="3">
-        <f> PSV78.001 plocha 78.2 m²</f>
+        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
         <v/>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -9669,7 +9673,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>PSV78.002a</t>
+          <t>PSV78.001b</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -9689,7 +9693,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
+          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -9698,10 +9702,10 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="I154" s="3">
-        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
+        <f> PSV78.001 plocha 78.2 m²</f>
         <v/>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -9711,7 +9715,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -9727,7 +9731,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>PSV78.002b</t>
+          <t>PSV78.002a</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -9747,7 +9751,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -9759,7 +9763,7 @@
         <v>208.4</v>
       </c>
       <c r="I155" s="3">
-        <f> PSV78.002 plocha 208.4 m²</f>
+        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
         <v/>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -9785,7 +9789,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>PSV78.003a</t>
+          <t>PSV78.002b</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -9805,7 +9809,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -9814,10 +9818,10 @@
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="I156" s="3">
-        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
+        <f> PSV78.002 plocha 208.4 m²</f>
         <v/>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -9827,7 +9831,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -9843,7 +9847,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>PSV78.003b</t>
+          <t>PSV78.003a</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -9863,7 +9867,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -9875,7 +9879,7 @@
         <v>201.6</v>
       </c>
       <c r="I157" s="3">
-        <f> PSV78.003 plocha 201.6 m²</f>
+        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
         <v/>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -9901,7 +9905,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>PSV78.004a</t>
+          <t>PSV78.003b</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -9921,7 +9925,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -9930,10 +9934,10 @@
         </is>
       </c>
       <c r="H158" s="2" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="I158" s="3">
-        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
+        <f> PSV78.003 plocha 201.6 m²</f>
         <v/>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -9943,7 +9947,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -9959,7 +9963,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>PSV78.004b</t>
+          <t>PSV78.004a</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -9979,7 +9983,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -9991,7 +9995,7 @@
         <v>179.1</v>
       </c>
       <c r="I159" s="3">
-        <f> PSV78.004 plocha 179.1 m²</f>
+        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
         <v/>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -10017,7 +10021,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>PSV78.005</t>
+          <t>PSV78.004b</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -10037,7 +10041,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -10046,26 +10050,25 @@
         </is>
       </c>
       <c r="H160" s="2" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
-        </is>
+        <v>179.1</v>
+      </c>
+      <c r="I160" s="3">
+        <f> PSV78.004 plocha 179.1 m²</f>
+        <v/>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
@@ -10076,7 +10079,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>PSV78.006</t>
+          <t>PSV78.005</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -10096,7 +10099,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10105,11 +10108,11 @@
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -10119,7 +10122,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
@@ -10135,7 +10138,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>PSV78.007</t>
+          <t>PSV78.006</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -10155,7 +10158,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -10164,11 +10167,11 @@
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -10178,7 +10181,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -10194,7 +10197,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>PSV78.008</t>
+          <t>PSV78.007</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -10214,7 +10217,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -10223,21 +10226,21 @@
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
@@ -10253,7 +10256,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>PSV78.009</t>
+          <t>PSV78.008</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -10273,7 +10276,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -10282,11 +10285,11 @@
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -10296,7 +10299,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -10312,7 +10315,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>PSV78.010</t>
+          <t>PSV78.009</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -10332,7 +10335,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -10341,11 +10344,11 @@
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -10355,7 +10358,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -10371,7 +10374,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>PSV78.011</t>
+          <t>PSV78.010</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -10391,7 +10394,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -10400,11 +10403,11 @@
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -10414,7 +10417,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -10430,7 +10433,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012</t>
+          <t>PSV78.011</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -10450,7 +10453,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -10459,21 +10462,21 @@
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
@@ -10489,7 +10492,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>PSV95.001</t>
+          <t>PSV78.012</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -10499,45 +10502,45 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
+          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr"/>
@@ -10548,7 +10551,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>PSV95.002</t>
+          <t>PSV95.001</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -10568,7 +10571,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -10577,26 +10580,26 @@
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ — min. 1 ks 34A</t>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr"/>
@@ -10607,27 +10610,27 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>PSV76.001</t>
+          <t>PSV95.002</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -10640,17 +10643,17 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -10666,7 +10669,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>PSV77.001</t>
+          <t>PSV76.001</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -10676,48 +10679,48 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
-        <v>17.6</v>
+        <v>1</v>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr"/>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>766682111</t>
+        </is>
+      </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -10725,58 +10728,58 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>PSV72.001</t>
+          <t>PSV77.001</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>1</v>
+        <v>17.6</v>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>722290515</t>
-        </is>
-      </c>
+          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
-        </is>
-      </c>
-      <c r="M172" s="2" t="inlineStr"/>
+          <t>wrong_leaf_disambiguation_needed</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -10784,7 +10787,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>PSV72.002</t>
+          <t>PSV72.001</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -10804,30 +10807,30 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
+          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
@@ -10843,7 +10846,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>PSV72.003</t>
+          <t>PSV72.002</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -10863,7 +10866,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -10872,26 +10875,26 @@
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
+          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr"/>
@@ -10902,7 +10905,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004a</t>
+          <t>PSV72.003</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -10922,35 +10925,35 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Vana — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>1× vana (DXF sanit_vana)</t>
+          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr"/>
@@ -10961,7 +10964,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004b</t>
+          <t>PSV72.004a</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -10981,7 +10984,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>Vana — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -10994,7 +10997,7 @@
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
+          <t>1× vana (DXF sanit_vana)</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -11020,7 +11023,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004c</t>
+          <t>PSV72.004b</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -11040,7 +11043,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -11053,7 +11056,7 @@
       </c>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>1× WC (TZ standard)</t>
+          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -11079,7 +11082,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005a</t>
+          <t>PSV72.004c</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -11099,7 +11102,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -11112,7 +11115,7 @@
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (DXF)</t>
+          <t>1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -11122,7 +11125,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -11138,7 +11141,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005b</t>
+          <t>PSV72.005a</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -11158,7 +11161,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -11171,7 +11174,7 @@
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>1× WC (TZ standard)</t>
+          <t>1× umyvadlo (DXF)</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -11197,7 +11200,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005c</t>
+          <t>PSV72.005b</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -11217,7 +11220,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -11230,7 +11233,7 @@
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>1× sprcha (TZ standard)</t>
+          <t>1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -11256,7 +11259,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006a</t>
+          <t>PSV72.005c</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -11276,7 +11279,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -11289,7 +11292,7 @@
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>1× WC (DXF)</t>
+          <t>1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -11299,7 +11302,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
@@ -11315,7 +11318,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006b</t>
+          <t>PSV72.006a</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -11335,7 +11338,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -11348,7 +11351,7 @@
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (TZ standard)</t>
+          <t>1× WC (DXF)</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -11374,7 +11377,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006c</t>
+          <t>PSV72.006b</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -11394,7 +11397,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -11407,7 +11410,7 @@
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>1× sprcha (TZ standard)</t>
+          <t>1× umyvadlo (TZ standard)</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -11433,7 +11436,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>PSV72.007</t>
+          <t>PSV72.006c</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -11453,7 +11456,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -11462,26 +11465,26 @@
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
+          <t>1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr"/>
@@ -11492,7 +11495,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008a</t>
+          <t>PSV72.007</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -11512,7 +11515,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Rohový ventil WC — dodávka + montáž</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -11521,26 +11524,26 @@
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
+          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr"/>
@@ -11551,7 +11554,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008b</t>
+          <t>PSV72.008a</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -11571,7 +11574,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Páková umyvadlová baterie — dodávka + montáž</t>
+          <t>Rohový ventil WC — dodávka + montáž</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -11584,7 +11587,7 @@
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
+          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -11610,7 +11613,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008c</t>
+          <t>PSV72.008b</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -11630,7 +11633,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Sprchová / vanová baterie termostatická — dodávka + montáž</t>
+          <t>Páková umyvadlová baterie — dodávka + montáž</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -11643,7 +11646,7 @@
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
+          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -11669,7 +11672,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008d</t>
+          <t>PSV72.008c</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -11689,7 +11692,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Dřezová baterie kuchyňská — dodávka + montáž</t>
+          <t>Sprchová / vanová baterie termostatická — dodávka + montáž</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -11698,11 +11701,11 @@
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>2× kuchyně (1.06 + 3.05)</t>
+          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -11728,7 +11731,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>PSV72.009</t>
+          <t>PSV72.008d</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -11748,7 +11751,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Dřezová baterie kuchyňská — dodávka + montáž</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -11757,26 +11760,26 @@
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
+          <t>2× kuchyně (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr"/>
@@ -11787,7 +11790,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>PSV72.010</t>
+          <t>PSV72.009</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -11807,7 +11810,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -11820,17 +11823,17 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
+          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -11846,7 +11849,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>PSV73.001</t>
+          <t>PSV72.010</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -11856,17 +11859,17 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -11879,17 +11882,17 @@
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
+          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
@@ -11905,7 +11908,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>PSV73.002</t>
+          <t>PSV73.001</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -11925,29 +11928,30 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H192" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I192" s="3">
-        <f> ks kamen</f>
-        <v/>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
+        </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -11963,7 +11967,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>PSV73.003</t>
+          <t>PSV73.002</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -11983,30 +11987,29 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
-        </is>
+      <c r="I193" s="3">
+        <f> ks kamen</f>
+        <v/>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -12022,7 +12025,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>PSV73.004</t>
+          <t>PSV73.003</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -12042,7 +12045,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -12055,17 +12058,17 @@
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
+          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -12081,7 +12084,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>PSV73.005</t>
+          <t>PSV73.004</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -12101,7 +12104,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -12114,17 +12117,17 @@
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
+          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
@@ -12140,7 +12143,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>PSV73.006</t>
+          <t>PSV73.005</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -12160,7 +12163,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -12169,21 +12172,21 @@
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
+          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -12199,7 +12202,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>PSV73.007</t>
+          <t>PSV73.006</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -12219,30 +12222,30 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — komín revize a úpravy stávajícího</t>
+          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="L197" s="2" t="inlineStr">
@@ -12258,7 +12261,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>PSV73.008</t>
+          <t>PSV73.007</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -12278,30 +12281,30 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
+          <t>TZ ARS — komín revize a úpravy stávajícího</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -12317,7 +12320,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>M21.001</t>
+          <t>PSV73.008</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -12327,40 +12330,40 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
+          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
@@ -12376,7 +12379,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>M21.002</t>
+          <t>M21.001</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -12396,30 +12399,30 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -12435,7 +12438,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>M21.003</t>
+          <t>M21.002</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -12455,30 +12458,30 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
@@ -12494,7 +12497,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>M21.004</t>
+          <t>M21.003</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -12514,30 +12517,30 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -12553,7 +12556,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>M21.005</t>
+          <t>M21.004</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -12573,7 +12576,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -12582,21 +12585,21 @@
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="L203" s="2" t="inlineStr">
@@ -12612,7 +12615,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>M21.006</t>
+          <t>M21.005</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -12632,30 +12635,30 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -12671,7 +12674,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>M21.007</t>
+          <t>M21.006</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -12691,7 +12694,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -12704,17 +12707,17 @@
       </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
@@ -12730,7 +12733,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>VRN.001</t>
+          <t>M21.007</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -12740,40 +12743,40 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -12789,7 +12792,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>VRN.002</t>
+          <t>VRN.001</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -12809,12 +12812,12 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="H207" s="2" t="n">
@@ -12822,17 +12825,17 @@
       </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>1 ks × 8 měs realizace</t>
+          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -12848,7 +12851,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>VRN.003</t>
+          <t>VRN.002</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -12868,30 +12871,30 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>Komplexní zřízení + provoz po dobu stavby</t>
+          <t>1 ks × 8 měs realizace</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -12907,7 +12910,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>VRN.101</t>
+          <t>VRN.003</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -12917,40 +12920,40 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H209" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
+          <t>Komplexní zřízení + provoz po dobu stavby</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -12966,7 +12969,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>VRN.201</t>
+          <t>VRN.101</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -12976,40 +12979,40 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>realizace ~8 měs</t>
+          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -13025,7 +13028,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>VRN.301</t>
+          <t>VRN.201</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -13035,22 +13038,22 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
@@ -13058,17 +13061,17 @@
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
+          <t>realizace ~8 měs</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
@@ -13084,7 +13087,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>VRN.302</t>
+          <t>VRN.301</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -13104,12 +13107,12 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
@@ -13117,17 +13120,17 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
+          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -13143,7 +13146,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>VRN.401</t>
+          <t>VRN.302</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -13153,17 +13156,17 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -13176,17 +13179,17 @@
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
+          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="L213" s="2" t="inlineStr">
@@ -13202,7 +13205,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>VRN.402</t>
+          <t>VRN.401</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -13222,7 +13225,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -13235,17 +13238,17 @@
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
+          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -13261,7 +13264,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>VRN.501</t>
+          <t>VRN.402</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -13271,17 +13274,17 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -13290,21 +13293,21 @@
         </is>
       </c>
       <c r="H215" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>2 etapy geodet × 1 kpl</t>
+          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="L215" s="2" t="inlineStr">
@@ -13320,7 +13323,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>VRN.601</t>
+          <t>VRN.501</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -13330,17 +13333,17 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -13349,21 +13352,21 @@
         </is>
       </c>
       <c r="H216" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>Standard — DSP pro kolaudaci</t>
+          <t>2 etapy geodet × 1 kpl</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -13379,7 +13382,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>VRN.701</t>
+          <t>VRN.601</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -13389,17 +13392,17 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -13412,17 +13415,17 @@
       </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
+          <t>Standard — DSP pro kolaudaci</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="L217" s="2" t="inlineStr">
@@ -13438,7 +13441,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>VRN.801</t>
+          <t>VRN.701</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -13448,22 +13451,22 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
@@ -13471,17 +13474,17 @@
       </c>
       <c r="I218" s="3" t="inlineStr">
         <is>
-          <t>Standard — paušál kolaudace</t>
+          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -13497,7 +13500,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>VRN.102</t>
+          <t>VRN.801</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -13507,17 +13510,17 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -13530,17 +13533,17 @@
       </c>
       <c r="I219" s="3" t="inlineStr">
         <is>
-          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
+          <t>Standard — paušál kolaudace</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -13556,7 +13559,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>VRN.103</t>
+          <t>VRN.102</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -13576,30 +13579,30 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>56.9</v>
+        <v>1</v>
       </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
+          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -13615,12 +13618,12 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>VRN.001</t>
+          <t>VRN.103</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -13635,30 +13638,30 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>1</v>
+        <v>56.9</v>
       </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
+          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="L221" s="2" t="inlineStr">
@@ -13674,7 +13677,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>VRN.002</t>
+          <t>VRN.001</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -13694,30 +13697,30 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
+          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
@@ -13733,7 +13736,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>VRN.101</t>
+          <t>VRN.002</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -13743,40 +13746,40 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="L223" s="2" t="inlineStr">
@@ -13792,7 +13795,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>VRN.201</t>
+          <t>VRN.101</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -13802,22 +13805,22 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
@@ -13825,17 +13828,17 @@
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="L224" s="2" t="inlineStr">
@@ -13851,55 +13854,55 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>HSV6.013</t>
+          <t>VRN.201</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>VRN — Společné</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>VRN — Společné</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>030001000</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
         </is>
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr"/>
@@ -13910,7 +13913,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>HSV6.014</t>
+          <t>HSV6.013</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -13930,7 +13933,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -13939,11 +13942,11 @@
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
@@ -13953,7 +13956,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
@@ -13969,7 +13972,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>HSV6.015</t>
+          <t>HSV6.014</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -13989,7 +13992,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -13998,26 +14001,26 @@
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I227" s="3" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>carried_verified</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr"/>
@@ -14028,7 +14031,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>PSV76.013</t>
+          <t>HSV6.015</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -14038,17 +14041,17 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -14057,21 +14060,21 @@
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
@@ -14087,7 +14090,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>VRN.020</t>
+          <t>PSV76.013</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -14097,22 +14100,22 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
@@ -14120,17 +14123,17 @@
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="L229" s="2" t="inlineStr">
@@ -14146,7 +14149,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>PSV76.014</t>
+          <t>VRN.020</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -14156,40 +14159,40 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="L230" s="2" t="inlineStr">
@@ -14205,7 +14208,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.A</t>
+          <t>PSV76.014</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -14215,17 +14218,17 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -14234,21 +14237,21 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I231" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="L231" s="2" t="inlineStr">
@@ -14264,7 +14267,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.B</t>
+          <t>PSV72.004.A</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -14284,7 +14287,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -14302,7 +14305,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -14323,7 +14326,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.C</t>
+          <t>PSV72.004.B</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -14343,7 +14346,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -14361,7 +14364,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -14382,7 +14385,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.A</t>
+          <t>PSV72.004.C</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -14402,7 +14405,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -14415,17 +14418,17 @@
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L234" s="2" t="inlineStr">
@@ -14441,7 +14444,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.B</t>
+          <t>PSV72.005.A</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -14461,7 +14464,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -14479,7 +14482,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -14500,7 +14503,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.C</t>
+          <t>PSV72.005.B</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -14520,7 +14523,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -14538,7 +14541,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -14559,7 +14562,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.A</t>
+          <t>PSV72.005.C</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -14579,7 +14582,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -14592,7 +14595,7 @@
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -14602,7 +14605,7 @@
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L237" s="2" t="inlineStr">
@@ -14618,7 +14621,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.B</t>
+          <t>PSV72.006.A</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -14638,7 +14641,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -14656,7 +14659,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -14677,7 +14680,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.C</t>
+          <t>PSV72.006.B</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -14697,7 +14700,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -14715,7 +14718,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
@@ -14736,7 +14739,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.1_PP</t>
+          <t>PSV72.006.C</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -14746,40 +14749,40 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -14795,7 +14798,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.1_NP</t>
+          <t>PSV78.012.1_PP</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -14815,7 +14818,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -14824,11 +14827,11 @@
         </is>
       </c>
       <c r="H241" s="2" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
-          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -14838,7 +14841,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="L241" s="2" t="inlineStr">
@@ -14854,7 +14857,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.2_NP</t>
+          <t>PSV78.012.1_NP</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -14874,7 +14877,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -14883,11 +14886,11 @@
         </is>
       </c>
       <c r="H242" s="2" t="n">
-        <v>247.5</v>
+        <v>254.5</v>
       </c>
       <c r="I242" s="3" t="inlineStr">
         <is>
-          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -14897,7 +14900,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="L242" s="2" t="inlineStr">
@@ -14913,7 +14916,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.3_NP</t>
+          <t>PSV78.012.2_NP</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -14933,7 +14936,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -14942,11 +14945,11 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="I243" s="3" t="inlineStr">
         <is>
-          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -14956,7 +14959,7 @@
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="L243" s="2" t="inlineStr">
@@ -14972,7 +14975,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>HSV6.016</t>
+          <t>PSV78.012.3_NP</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -14982,45 +14985,45 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H244" s="2" t="n">
-        <v>0.6</v>
+        <v>219.3</v>
       </c>
       <c r="I244" s="3" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr"/>
@@ -15031,7 +15034,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>HSV6.017</t>
+          <t>HSV6.016</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -15051,7 +15054,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -15060,21 +15063,21 @@
         </is>
       </c>
       <c r="H245" s="2" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
@@ -15090,7 +15093,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015a</t>
+          <t>HSV6.017</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -15100,44 +15103,45 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I246" s="3">
-        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="I246" s="3" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr"/>
@@ -15148,7 +15152,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015b</t>
+          <t>HSV1.015a</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -15168,7 +15172,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
+          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -15180,7 +15184,7 @@
         <v>12</v>
       </c>
       <c r="I247" s="3">
-        <f> HSV1.015 délka drenáže 12 m</f>
+        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
         <v/>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -15206,7 +15210,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015c</t>
+          <t>HSV1.015b</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -15226,7 +15230,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -15238,12 +15242,12 @@
         <v>12</v>
       </c>
       <c r="I248" s="3">
-        <f> HSV1.015 délka 12 m</f>
+        <f> HSV1.015 délka drenáže 12 m</f>
         <v/>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>212</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -15264,62 +15268,57 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>HSV5.001</t>
+          <t>HSV1.015c</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H249" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I249" s="3" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="I249" s="3">
+        <f> HSV1.015 délka 12 m</f>
+        <v/>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>693</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
         </is>
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+          <t>family_only</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -15327,46 +15326,50 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>VRN.PM01</t>
+          <t>HSV5.001</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I250" s="3" t="inlineStr">
         <is>
-          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
-        </is>
-      </c>
-      <c r="J250" s="2" t="inlineStr"/>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>121301101</t>
+        </is>
+      </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -15374,7 +15377,11 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -15382,7 +15389,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>VRN.PM02</t>
+          <t>VRN.PM01</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -15392,36 +15399,36 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>503.1</v>
+        <v>0</v>
       </c>
       <c r="I251" s="3" t="inlineStr">
         <is>
-          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
+          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
@@ -15437,7 +15444,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>HSV1.016</t>
+          <t>VRN.PM02</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -15447,48 +15454,44 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>13</v>
+        <v>503.1</v>
       </c>
       <c r="I252" s="3" t="inlineStr">
         <is>
-          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
+          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>Situace měření 2026-05-29 (rameno 8×175×280 + rameno 5×175×280) + TZ statika §3.2.5 'schody na terénu z betonových dílců do betonového lože'</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
-        </is>
-      </c>
-      <c r="M252" s="2" t="inlineStr">
-        <is>
-          <t>Venkovní schody na terénu</t>
-        </is>
-      </c>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -15496,7 +15499,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017a</t>
+          <t>HSV1.016</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -15506,17 +15509,17 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
+          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -15525,30 +15528,27 @@
         </is>
       </c>
       <c r="H253" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I253" s="3">
-        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
-        <v/>
-      </c>
-      <c r="J253" s="2" t="inlineStr">
-        <is>
-          <t>762085112</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I253" s="3" t="inlineStr">
+        <is>
+          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
+          <t>Situace měření 2026-05-29 (rameno 8×175×280 + rameno 5×175×280) + TZ statika §3.2.5 'schody na terénu z betonových dílců do betonového lože'</t>
         </is>
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>Krov — spojovací prostředky</t>
+          <t>Venkovní schody na terénu</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017b</t>
+          <t>HSV5.017a</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -15578,24 +15578,24 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
+          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I254" s="3">
-        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
+        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
         <v/>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>31197004</t>
+          <t>762085112</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>carried_verified</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017c</t>
+          <t>HSV5.017b</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -15640,24 +15640,24 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
+          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>100 ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I255" s="3">
-        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
+        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
         <v/>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>3111006</t>
+          <t>31197004</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017d</t>
+          <t>HSV5.017c</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
+          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>31121004</t>
+          <t>3111006</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>HSV4.015a</t>
+          <t>HSV5.017d</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -15754,39 +15754,39 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
+          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>100 ks</t>
         </is>
       </c>
       <c r="H257" s="2" t="n">
-        <v>59.5</v>
+        <v>1</v>
       </c>
       <c r="I257" s="3">
-        <f> plocha stropu S07</f>
+        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
         <v/>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>713191</t>
+          <t>31121004</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="L257" s="2" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>Krov — spojovací prostředky</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>HSV4.015b</t>
+          <t>HSV4.015a</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
+          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -15835,13 +15835,17 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>62.5</v>
+        <v>59.5</v>
       </c>
       <c r="I258" s="3">
-        <f> 59.5 × 1.05 prořez</f>
+        <f> plocha stropu S07</f>
         <v/>
       </c>
-      <c r="J258" s="2" t="inlineStr"/>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>713191</t>
+        </is>
+      </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
           <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
@@ -15849,7 +15853,7 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
@@ -15864,7 +15868,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>HSV4.016a</t>
+          <t>HSV4.015b</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -15884,7 +15888,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
+          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -15893,16 +15897,16 @@
         </is>
       </c>
       <c r="H259" s="2" t="n">
-        <v>65.5</v>
+        <v>62.5</v>
       </c>
       <c r="I259" s="3">
-        <f> 59.5 × 1.10 přesahy</f>
+        <f> 59.5 × 1.05 prořez</f>
         <v/>
       </c>
       <c r="J259" s="2" t="inlineStr"/>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — separační geotextilie</t>
+          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
         </is>
       </c>
       <c r="L259" s="2" t="inlineStr">
@@ -15922,7 +15926,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>HSV4.017a</t>
+          <t>HSV4.016a</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -15942,7 +15946,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
+          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -15951,30 +15955,26 @@
         </is>
       </c>
       <c r="H260" s="2" t="n">
-        <v>104.4</v>
+        <v>65.5</v>
       </c>
       <c r="I260" s="3">
-        <f> plocha stropu S09</f>
+        <f> 59.5 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="J260" s="2" t="inlineStr">
-        <is>
-          <t>713121</t>
-        </is>
-      </c>
+      <c r="J260" s="2" t="inlineStr"/>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
+          <t>skladba S07 návrh — separační geotextilie</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S07</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>HSV4.017b</t>
+          <t>HSV4.017a</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Minerální vata 180/200 mm — materiál</t>
+          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -16013,13 +16013,17 @@
         </is>
       </c>
       <c r="H261" s="2" t="n">
-        <v>109.6</v>
+        <v>104.4</v>
       </c>
       <c r="I261" s="3">
-        <f> 104.4 × 1.05</f>
+        <f> plocha stropu S09</f>
         <v/>
       </c>
-      <c r="J261" s="2" t="inlineStr"/>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>713121</t>
+        </is>
+      </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
           <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
@@ -16027,7 +16031,7 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
@@ -16042,7 +16046,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>HSV4.018a</t>
+          <t>HSV4.017b</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -16062,7 +16066,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
+          <t>Minerální vata 180/200 mm — materiál</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -16070,20 +16074,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H262" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I262" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — V1</t>
-        </is>
+      <c r="H262" s="2" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="I262" s="3">
+        <f> 104.4 × 1.05</f>
+        <v/>
       </c>
       <c r="J262" s="2" t="inlineStr"/>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda (řez nepretíná, plocha nepřiřazena)</t>
+          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
@@ -16093,7 +16094,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S09</t>
         </is>
       </c>
     </row>
@@ -16103,7 +16104,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>HSV4.019a</t>
+          <t>HSV4.018a</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -16123,7 +16124,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
+          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -16141,14 +16142,10 @@
           <t>neurčeno — V1</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr">
-        <is>
-          <t>713191</t>
-        </is>
-      </c>
+      <c r="J263" s="2" t="inlineStr"/>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda</t>
+          <t>skladba S08 legenda (řez nepretíná, plocha nepřiřazena)</t>
         </is>
       </c>
       <c r="L263" s="2" t="inlineStr">
@@ -16168,7 +16165,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>HSV4.020a</t>
+          <t>HSV4.019a</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -16188,7 +16185,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
+          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -16206,7 +16203,11 @@
           <t>neurčeno — V1</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr"/>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>713191</t>
+        </is>
+      </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
           <t>skladba S08 legenda</t>
@@ -16229,7 +16230,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>HSV4.021a</t>
+          <t>HSV4.020a</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -16249,7 +16250,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Separační vrstva — S08 (neurčeno)</t>
+          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -16290,7 +16291,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>HSV7.007a</t>
+          <t>HSV4.021a</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -16300,17 +16301,17 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+          <t>Separační vrstva — S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -16318,17 +16319,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H266" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I266" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
-        <v/>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>skladba S08 legenda</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -16338,7 +16342,7 @@
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S08</t>
         </is>
       </c>
     </row>
@@ -16348,7 +16352,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>HSV7.007b</t>
+          <t>HSV7.007a</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16368,7 +16372,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -16377,10 +16381,10 @@
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I267" s="3">
-        <f> 23 × 1.05</f>
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
@@ -16406,7 +16410,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>HSV7.008a</t>
+          <t>HSV7.007b</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -16426,7 +16430,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -16435,16 +16439,16 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I268" s="3">
-        <f> 23 × 1.10</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A/C-C sokl + obvod ETICS</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -16464,7 +16468,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>HSV7.009a</t>
+          <t>HSV7.008a</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -16484,7 +16488,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -16493,16 +16497,16 @@
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I269" s="3">
-        <f> 23 (OVĚŘIT)</f>
+        <f> 23 × 1.10</f>
         <v/>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>Řez A-A/C-C sokl + obvod ETICS</t>
         </is>
       </c>
       <c r="L269" s="2" t="inlineStr">
@@ -16522,7 +16526,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>HSV7.009b</t>
+          <t>HSV7.009a</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -16542,7 +16546,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
+          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -16551,17 +16555,13 @@
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I270" s="3">
-        <f> 23 × 1.05</f>
+        <f> 23 (OVĚŘIT)</f>
         <v/>
       </c>
-      <c r="J270" s="2" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
+      <c r="J270" s="2" t="inlineStr"/>
       <c r="K270" s="3" t="inlineStr">
         <is>
           <t>Řez A-A sokl tags S03b + obvod ETICS</t>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M270" s="2" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>HSV5.018a</t>
+          <t>HSV7.009b</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -16594,17 +16594,17 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
+          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -16613,26 +16613,30 @@
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="I271" s="3">
-        <f> 140.94 × 1.10 přesahy</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
-      <c r="J271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>skladba S10 návrh — pojistná HI pod Al krytinu</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16646,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>HSV6.018a</t>
+          <t>HSV5.018a</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -16652,17 +16656,17 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
+          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -16671,16 +16675,16 @@
         </is>
       </c>
       <c r="H272" s="2" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="I272" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> 140.94 × 1.10 přesahy</f>
         <v/>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
+          <t>skladba S10 návrh — pojistná HI pod Al krytinu</t>
         </is>
       </c>
       <c r="L272" s="2" t="inlineStr">
@@ -16690,7 +16694,7 @@
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S10</t>
         </is>
       </c>
     </row>
@@ -16700,27 +16704,27 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002a</t>
+          <t>HSV6.018a</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>HSV 5 Komunikace pozemní — dlažby</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -16728,20 +16732,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H273" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I273" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
-        </is>
+      <c r="H273" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I273" s="3">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
       <c r="K273" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
         </is>
       </c>
       <c r="L273" s="2" t="inlineStr">
@@ -16749,7 +16750,11 @@
           <t>needs_lookup</t>
         </is>
       </c>
-      <c r="M273" s="2" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -16757,7 +16762,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002b</t>
+          <t>HSV5.002a</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -16777,7 +16782,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -16792,7 +16797,7 @@
       </c>
       <c r="I274" s="3" t="inlineStr">
         <is>
-          <t>neurčeno — OVĚŘIT</t>
+          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
@@ -16814,7 +16819,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002c</t>
+          <t>HSV5.002b</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -16834,12 +16839,12 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -16871,7 +16876,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>PSV76.002a</t>
+          <t>HSV5.002c</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -16881,35 +16886,38 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>PSV 767 zámečnické konstrukce</t>
+          <t>HSV 5 Komunikace pozemní — dlažby</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Vjezdová brána ocelová — dodávka + montáž</t>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="H276" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I276" s="3">
-        <f> 1 brána</f>
-        <v/>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="L276" s="2" t="inlineStr">
@@ -16925,7 +16933,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>VRN.003a</t>
+          <t>PSV76.002a</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -16935,35 +16943,35 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>VRN geodetické + zaměřovací práce</t>
+          <t>PSV 767 zámečnické konstrukce</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
+          <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H277" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I277" s="3">
-        <f> 1 soubor</f>
+        <f> 1 brána</f>
         <v/>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
       <c r="K277" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="L277" s="2" t="inlineStr">
@@ -16979,45 +16987,45 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>M24.001a</t>
+          <t>VRN.003a</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>M-24 VZT</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>M / 751 vzduchotechnika — odtah digestoře</t>
+          <t>VRN geodetické + zaměřovací práce</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Lokální odtah digestoře kuchyně + prostup + zpětná klapka</t>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I278" s="3">
-        <f> 2 kuchyně (1.NP + 3.NP)</f>
+        <f> 1 soubor</f>
         <v/>
       </c>
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr">
@@ -17033,7 +17041,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>M21.008a</t>
+          <t>M24.001a</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -17043,35 +17051,35 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
+          <t>M / 751 vzduchotechnika — odtah digestoře</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
+          <t>Lokální odtah digestoře kuchyně + prostup + zpětná klapka</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H279" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I279" s="3">
-        <f> 1 soubor</f>
+        <f> 2 kuchyně (1.NP + 3.NP)</f>
         <v/>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
       <c r="K279" s="3" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="L279" s="2" t="inlineStr">
@@ -17087,7 +17095,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>M21.008b</t>
+          <t>M21.008a</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -17107,7 +17115,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -17141,7 +17149,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>PSV95.003a</t>
+          <t>M21.008b</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -17151,17 +17159,17 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>VRN doklady / revize požární</t>
+          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -17179,18 +17187,72 @@
       <c r="J281" s="2" t="inlineStr"/>
       <c r="K281" s="3" t="inlineStr">
         <is>
+          <t>PBŘ D.3 §16.05/16.06</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>PSV95.003a</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>PSV-95 Detekce požární</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>VRN doklady / revize požární</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" s="3">
+        <f> 1 soubor</f>
+        <v/>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
           <t>PBŘ D.3</t>
         </is>
       </c>
-      <c r="L281" s="2" t="inlineStr">
+      <c r="L282" s="2" t="inlineStr">
         <is>
           <t>needs_lookup</t>
         </is>
       </c>
-      <c r="M281" s="2" t="inlineStr"/>
+      <c r="M282" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M281"/>
+  <autoFilter ref="A1:M282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$280</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M282"/>
+  <dimension ref="A1:M280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>HSV7.003a</t>
+          <t>HSV7.004a</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -7154,29 +7154,29 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Lepení + kotvení desek XPS λ=0.034 tl. 120 mm + soklový profil — ETICS sokl</t>
+          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="I111" s="3">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.004 obvod špalet 82.2 bm</f>
         <v/>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>622</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>HSV7.003b</t>
+          <t>HSV7.004b</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -7216,29 +7216,29 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Cihelný obklad soklu spárovaný (na armovací vrstvu)</t>
+          <t>Špalety oken — armovací vrstva síťka + omítka</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="I112" s="3">
-        <f> HSV7.003 plocha soklu 13.5 m²</f>
+        <f> HSV7.004 obvod 82.2 bm</f>
         <v/>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>622</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>HSV7.004a</t>
+          <t>HSV7.005</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -7278,34 +7278,35 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm lepení + kotvení</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="I113" s="3">
-        <f> HSV7.004 obvod špalet 82.2 bm</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>paušál — dle pohledů NCS NZÚ</t>
+        </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -7320,7 +7321,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>HSV7.004b</t>
+          <t>HSV7.006</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -7340,39 +7341,40 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Špalety oken — armovací vrstva síťka + omítka</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="I114" s="3">
-        <f> HSV7.004 obvod 82.2 bm</f>
-        <v/>
+        <v>276.7</v>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>ETICS fasáda 276.7 m² (sokl = keramický obklad S03, NE omítka)</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01, S12a, S12b</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7384,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>HSV7.005</t>
+          <t>PSV71.001</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -7392,52 +7394,48 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>1</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
+          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
+          <t>FAMILY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -7445,7 +7443,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>HSV7.006</t>
+          <t>PSV71.002</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -7455,40 +7453,40 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>290.2</v>
+        <v>12</v>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -7496,11 +7494,7 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7508,7 +7502,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>PSV71.001</t>
+          <t>PSV71.003</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -7528,7 +7522,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -7537,21 +7531,17 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>712311101</t>
-        </is>
-      </c>
+          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -7567,7 +7557,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>PSV71.002</t>
+          <t>PSV71.101</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7577,40 +7567,36 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>12</v>
+        <v>177.5</v>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>712381111</t>
-        </is>
-      </c>
+          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -7626,7 +7612,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>PSV71.003</t>
+          <t>PSV71.102</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -7636,17 +7622,17 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -7655,17 +7641,16 @@
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
-        </is>
+        <v>104.4</v>
+      </c>
+      <c r="I119" s="3">
+        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
+        <v/>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -7673,7 +7658,11 @@
           <t>FAMILY_VERIFIED</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -7681,7 +7670,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PSV71.101</t>
+          <t>PSV76.001</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7691,36 +7680,40 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>177.5</v>
+        <v>2</v>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr"/>
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>766621011</t>
+        </is>
+      </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -7736,7 +7729,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>PSV71.102</t>
+          <t>PSV76.002</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7746,47 +7739,48 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="I121" s="3">
-        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
-        <v/>
-      </c>
-      <c r="J121" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>766621011</t>
+        </is>
+      </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
-        </is>
-      </c>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7794,7 +7788,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PSV76.001</t>
+          <t>PSV76.003</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7814,7 +7808,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -7823,11 +7817,11 @@
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -7837,12 +7831,12 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr"/>
@@ -7853,7 +7847,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>PSV76.002</t>
+          <t>PSV76.004</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7873,7 +7867,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -7886,7 +7880,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -7896,7 +7890,7 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -7912,7 +7906,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>PSV76.003</t>
+          <t>PSV76.005</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7932,7 +7926,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -7941,11 +7935,11 @@
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -7955,7 +7949,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -7971,7 +7965,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PSV76.004</t>
+          <t>PSV76.006</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7991,7 +7985,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -8000,11 +7994,11 @@
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -8014,7 +8008,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -8030,7 +8024,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>PSV76.005</t>
+          <t>PSV76.007</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -8050,7 +8044,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -8059,11 +8053,11 @@
         </is>
       </c>
       <c r="H126" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -8073,7 +8067,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -8089,7 +8083,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>PSV76.006</t>
+          <t>PSV76.008</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -8109,7 +8103,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -8118,21 +8112,21 @@
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -8148,7 +8142,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>PSV76.007</t>
+          <t>PSV76.009</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -8168,7 +8162,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -8181,17 +8175,17 @@
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+          <t>TZ ARS — vstupní plastové dveře</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -8207,7 +8201,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>PSV76.008</t>
+          <t>PSV76.010</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -8227,7 +8221,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8236,21 +8230,21 @@
         </is>
       </c>
       <c r="H129" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -8266,7 +8260,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>PSV76.009</t>
+          <t>PSV76.101</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -8276,45 +8270,45 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>2</v>
+        <v>69.5</v>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — vstupní plastové dveře</t>
+          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr"/>
@@ -8325,7 +8319,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>PSV76.010</t>
+          <t>PSV76.102</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -8335,45 +8329,44 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H131" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
-        <is>
-          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
-        </is>
+        <v>20.8</v>
+      </c>
+      <c r="I131" s="3">
+        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
+        <v/>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr"/>
@@ -8384,7 +8377,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>PSV76.101</t>
+          <t>PSV76.103a</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -8404,7 +8397,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Dešťové svody Pzn Ø100 mm — 4 svody</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -8413,26 +8406,26 @@
         </is>
       </c>
       <c r="H132" s="2" t="n">
-        <v>69.5</v>
+        <v>28</v>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
+          <t>4 svody × ~7 m výška = 28 bm</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr"/>
@@ -8443,7 +8436,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>PSV76.102</t>
+          <t>PSV76.103b</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -8463,7 +8456,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Podokapní žlaby Pzn — po obvodu střechy</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -8472,25 +8465,25 @@
         </is>
       </c>
       <c r="H133" s="2" t="n">
-        <v>20.8</v>
+        <v>15.5</v>
       </c>
       <c r="I133" s="3">
-        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
+        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
         <v/>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr"/>
@@ -8501,7 +8494,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>PSV76.103a</t>
+          <t>PSV76.104</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -8521,7 +8514,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn Ø100 mm — 4 svody</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -8530,26 +8523,26 @@
         </is>
       </c>
       <c r="H134" s="2" t="n">
-        <v>28</v>
+        <v>26.1</v>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>4 svody × ~7 m výška = 28 bm</t>
+          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr"/>
@@ -8560,7 +8553,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>PSV76.103b</t>
+          <t>PSV76.201</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -8570,44 +8563,45 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Podokapní žlaby Pzn — po obvodu střechy</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H135" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I135" s="3">
-        <f> PSV76.003 celkem 43.5 bm − svody 28 bm = 15.5 bm žlaby</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
+        </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr"/>
@@ -8618,7 +8612,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>PSV76.104</t>
+          <t>PSV76.202</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -8628,45 +8622,45 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H136" s="2" t="n">
-        <v>26.1</v>
+        <v>1</v>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED_CHAPTER_MATCH</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr"/>
@@ -8677,7 +8671,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>PSV76.201</t>
+          <t>PSV76.203</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -8697,35 +8691,35 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
+          <t>2 vstupy</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr"/>
@@ -8736,7 +8730,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>PSV76.202</t>
+          <t>PSV76.204</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -8756,35 +8750,35 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>1 schodiště do podkroví (TZ ARS)</t>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr"/>
@@ -8795,7 +8789,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>PSV76.203</t>
+          <t>PSV76.301</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -8805,17 +8799,17 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -8824,21 +8818,21 @@
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>2 vstupy</t>
+          <t>2 schodiště × ~8 stupňů = 16</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -8854,7 +8848,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>PSV76.204</t>
+          <t>PSV76.302a</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -8864,45 +8858,44 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
-        </is>
+        <v>9.23</v>
+      </c>
+      <c r="I140" s="3">
+        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
+        <v/>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>762</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr"/>
@@ -8913,7 +8906,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>PSV76.301</t>
+          <t>PSV76.302b</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -8933,35 +8926,34 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>2 schodiště × ~8 stupňů = 16</t>
-        </is>
+        <v>9.23</v>
+      </c>
+      <c r="I141" s="3">
+        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
+        <v/>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>762</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr"/>
@@ -8972,7 +8964,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>PSV76.302a</t>
+          <t>PSV77.001</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -8982,17 +8974,17 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Podkladní rošt z dřevěných hranolů 50 mm na rektifikovatelných terčích — terasa za opěrnou stěnou</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9001,25 +8993,26 @@
         </is>
       </c>
       <c r="H142" s="2" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="I142" s="3">
-        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
-        <v/>
+        <v>171.5</v>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
+        </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr"/>
@@ -9030,7 +9023,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>PSV76.302b</t>
+          <t>PSV77.002a</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -9040,17 +9033,17 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Terasová dřevěná prkna garapa 145×25 mm — montáž na dřevěný rošt, terasa za opěrnou stěnou</t>
+          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -9059,20 +9052,20 @@
         </is>
       </c>
       <c r="H143" s="2" t="n">
-        <v>9.23</v>
+        <v>13.5</v>
       </c>
       <c r="I143" s="3">
-        <f> PSV76.002 plocha terasy 9.23 m² (situace měření)</f>
+        <f> PSV77.002 plocha 13.5 m²</f>
         <v/>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>771</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
@@ -9088,7 +9081,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>PSV77.001</t>
+          <t>PSV77.002b</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -9108,7 +9101,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9117,26 +9110,25 @@
         </is>
       </c>
       <c r="H144" s="2" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
-        </is>
+        <v>13.5</v>
+      </c>
+      <c r="I144" s="3">
+        <f> PSV77.002 plocha 13.5 m²</f>
+        <v/>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr"/>
@@ -9147,7 +9139,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>PSV77.002a</t>
+          <t>PSV77.003a</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -9167,7 +9159,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace podkladu — koupelny + WC + spíž + komora</t>
+          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -9176,10 +9168,10 @@
         </is>
       </c>
       <c r="H145" s="2" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="I145" s="3">
-        <f> PSV77.002 plocha 13.5 m²</f>
+        <f> PSV77.003 plocha 32.4 m²</f>
         <v/>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -9189,7 +9181,7 @@
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
@@ -9205,7 +9197,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>PSV77.002b</t>
+          <t>PSV77.003b</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -9225,7 +9217,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — koupelny + WC + spíž + komora</t>
+          <t>Spárování keramické dlažby + úklid — 1.PP</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -9234,10 +9226,10 @@
         </is>
       </c>
       <c r="H146" s="2" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="I146" s="3">
-        <f> PSV77.002 plocha 13.5 m²</f>
+        <f> PSV77.003 plocha 32.4 m²</f>
         <v/>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -9247,7 +9239,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -9263,7 +9255,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>PSV77.003a</t>
+          <t>PSV77.004</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -9283,7 +9275,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Kladení keramické dlažby lepené + penetrace — 1.PP technické místnosti</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -9292,25 +9284,26 @@
         </is>
       </c>
       <c r="H147" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I147" s="3">
-        <f> PSV77.003 plocha 32.4 m²</f>
-        <v/>
+        <v>25</v>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
+        </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr"/>
@@ -9321,7 +9314,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>PSV77.003b</t>
+          <t>PSV77.005</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -9341,7 +9334,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Spárování keramické dlažby + úklid — 1.PP</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9350,25 +9343,26 @@
         </is>
       </c>
       <c r="H148" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I148" s="3">
-        <f> PSV77.003 plocha 32.4 m²</f>
-        <v/>
+        <v>126.4</v>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+        </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr"/>
@@ -9379,7 +9373,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>PSV77.004</t>
+          <t>PSV77.006</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -9399,30 +9393,30 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H149" s="2" t="n">
-        <v>25</v>
+        <v>72.03</v>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -9438,7 +9432,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>PSV77.005</t>
+          <t>PSV77.007</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -9458,30 +9452,30 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H150" s="2" t="n">
-        <v>126.4</v>
+        <v>19.28</v>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -9497,7 +9491,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>PSV77.006</t>
+          <t>PSV78.001a</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -9507,45 +9501,44 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H151" s="2" t="n">
-        <v>72.03</v>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
-        </is>
+        <v>78.2</v>
+      </c>
+      <c r="I151" s="3">
+        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
+        <v/>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr"/>
@@ -9556,7 +9549,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>PSV77.007</t>
+          <t>PSV78.001b</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -9566,45 +9559,44 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
-        </is>
+        <v>78.2</v>
+      </c>
+      <c r="I152" s="3">
+        <f> PSV78.001 plocha 78.2 m²</f>
+        <v/>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr"/>
@@ -9615,7 +9607,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>PSV78.001a</t>
+          <t>PSV78.002a</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -9635,7 +9627,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.PP (vč. vyspravení stávajících)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -9644,10 +9636,10 @@
         </is>
       </c>
       <c r="H153" s="2" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="I153" s="3">
-        <f> PSV78.001 plocha stěn 1.PP 78.2 m²</f>
+        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
         <v/>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -9657,7 +9649,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
@@ -9673,7 +9665,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>PSV78.001b</t>
+          <t>PSV78.002b</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -9693,7 +9685,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava (štuk) na jádrové omítce — stěny 1.PP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -9702,10 +9694,10 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="I154" s="3">
-        <f> PSV78.001 plocha 78.2 m²</f>
+        <f> PSV78.002 plocha 208.4 m²</f>
         <v/>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -9715,7 +9707,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -9731,7 +9723,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>PSV78.002a</t>
+          <t>PSV78.003a</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -9751,7 +9743,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 1.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -9760,10 +9752,10 @@
         </is>
       </c>
       <c r="H155" s="2" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="I155" s="3">
-        <f> PSV78.002 plocha stěn 1.NP 208.4 m²</f>
+        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
         <v/>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -9773,7 +9765,7 @@
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
@@ -9789,7 +9781,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>PSV78.002b</t>
+          <t>PSV78.003b</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -9809,7 +9801,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 1.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -9818,10 +9810,10 @@
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="I156" s="3">
-        <f> PSV78.002 plocha 208.4 m²</f>
+        <f> PSV78.003 plocha 201.6 m²</f>
         <v/>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -9831,7 +9823,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -9847,7 +9839,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>PSV78.003a</t>
+          <t>PSV78.004a</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -9867,7 +9859,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 2.NP</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -9876,10 +9868,10 @@
         </is>
       </c>
       <c r="H157" s="2" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="I157" s="3">
-        <f> PSV78.003 plocha stěn 2.NP 201.6 m²</f>
+        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
         <v/>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -9889,7 +9881,7 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -9905,7 +9897,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>PSV78.003b</t>
+          <t>PSV78.004b</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -9925,7 +9917,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 2.NP</t>
+          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -9934,10 +9926,10 @@
         </is>
       </c>
       <c r="H158" s="2" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="I158" s="3">
-        <f> PSV78.003 plocha 201.6 m²</f>
+        <f> PSV78.004 plocha 179.1 m²</f>
         <v/>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -9947,7 +9939,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -9963,7 +9955,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>PSV78.004a</t>
+          <t>PSV78.005</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -9983,7 +9975,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm na stěnách 3.NP</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -9992,25 +9984,26 @@
         </is>
       </c>
       <c r="H159" s="2" t="n">
-        <v>179.1</v>
-      </c>
-      <c r="I159" s="3">
-        <f> PSV78.004 plocha stěn 3.NP 179.1 m²</f>
-        <v/>
+        <v>59.5</v>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr"/>
@@ -10021,7 +10014,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>PSV78.004b</t>
+          <t>PSV78.006</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -10041,7 +10034,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Štuková povrchová úprava na jádrové omítce — stěny 3.NP</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -10050,25 +10043,26 @@
         </is>
       </c>
       <c r="H160" s="2" t="n">
-        <v>179.1</v>
-      </c>
-      <c r="I160" s="3">
-        <f> PSV78.004 plocha 179.1 m²</f>
-        <v/>
+        <v>61.1</v>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+        </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
@@ -10079,7 +10073,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>PSV78.005</t>
+          <t>PSV78.007</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -10099,7 +10093,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10108,11 +10102,11 @@
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>59.5</v>
+        <v>64.5</v>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -10122,7 +10116,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
@@ -10138,7 +10132,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>PSV78.006</t>
+          <t>PSV78.008</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -10158,7 +10152,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -10167,21 +10161,21 @@
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>61.1</v>
+        <v>13.4</v>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -10197,7 +10191,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>PSV78.007</t>
+          <t>PSV78.009</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -10217,7 +10211,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -10226,21 +10220,21 @@
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>64.5</v>
+        <v>15.2</v>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
@@ -10256,7 +10250,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>PSV78.008</t>
+          <t>PSV78.010</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -10276,7 +10270,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -10285,11 +10279,11 @@
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>13.4</v>
+        <v>24.3</v>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -10299,7 +10293,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -10315,7 +10309,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>PSV78.009</t>
+          <t>PSV78.011</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -10335,7 +10329,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -10344,11 +10338,11 @@
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>15.2</v>
+        <v>10</v>
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -10358,7 +10352,7 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -10374,7 +10368,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>PSV78.010</t>
+          <t>PSV78.012</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -10394,7 +10388,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -10403,21 +10397,21 @@
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -10433,7 +10427,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>PSV78.011</t>
+          <t>PSV95.001</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -10443,45 +10437,45 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I167" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr"/>
@@ -10492,7 +10486,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012</t>
+          <t>PSV95.002</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -10502,40 +10496,40 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>Σ ploch 1.NP+2.NP+3.NP × 2.5 (stěny per ratio) − obklady 70 + SDK podhledy = ~628 m²</t>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -10551,27 +10545,27 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>PSV95.001</t>
+          <t>PSV76.001</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -10580,26 +10574,26 @@
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
+          <t>1 ks vstupní dveře skladu</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr"/>
@@ -10610,58 +10604,58 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>PSV95.002</t>
+          <t>PSV77.001</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>1</v>
+        <v>17.6</v>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ — min. 1 ks 34A</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>966067121</t>
-        </is>
-      </c>
+          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M170" s="2" t="inlineStr"/>
+          <t>wrong_leaf_disambiguation_needed</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -10669,32 +10663,32 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>PSV76.001</t>
+          <t>PSV72.001</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
@@ -10702,22 +10696,22 @@
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr"/>
@@ -10728,58 +10722,58 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>PSV77.001</t>
+          <t>PSV72.002</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>17.6</v>
+        <v>80</v>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>722172011</t>
+        </is>
+      </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
-        </is>
-      </c>
-      <c r="M172" s="2" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
+          <t>FAMILY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -10787,7 +10781,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>PSV72.001</t>
+          <t>PSV72.003</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -10807,35 +10801,35 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
+          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr"/>
@@ -10846,7 +10840,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>PSV72.002</t>
+          <t>PSV72.004a</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -10866,35 +10860,35 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Vana — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
+          <t>1× vana (DXF sanit_vana)</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr"/>
@@ -10905,7 +10899,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>PSV72.003</t>
+          <t>PSV72.004b</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -10925,35 +10919,35 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
+          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr"/>
@@ -10964,7 +10958,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004a</t>
+          <t>PSV72.004c</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -10984,7 +10978,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Vana — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -10997,7 +10991,7 @@
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>1× vana (DXF sanit_vana)</t>
+          <t>1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -11023,7 +11017,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004b</t>
+          <t>PSV72.005a</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -11043,7 +11037,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -11056,7 +11050,7 @@
       </c>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (DXF sanit_umyvadlo)</t>
+          <t>1× umyvadlo (DXF)</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -11066,7 +11060,7 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
@@ -11082,7 +11076,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004c</t>
+          <t>PSV72.005b</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -11102,7 +11096,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 1.05 1.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -11125,7 +11119,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -11141,7 +11135,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005a</t>
+          <t>PSV72.005c</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -11161,7 +11155,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -11174,7 +11168,7 @@
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (DXF)</t>
+          <t>1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -11200,7 +11194,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005b</t>
+          <t>PSV72.006a</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -11220,7 +11214,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -11233,7 +11227,7 @@
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>1× WC (TZ standard)</t>
+          <t>1× WC (DXF)</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
@@ -11243,7 +11237,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -11259,7 +11253,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005c</t>
+          <t>PSV72.006b</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -11279,7 +11273,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 2.03 2.NP</t>
+          <t>Umyvadlo — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -11292,7 +11286,7 @@
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>1× sprcha (TZ standard)</t>
+          <t>1× umyvadlo (TZ standard)</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -11302,7 +11296,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
@@ -11318,7 +11312,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006a</t>
+          <t>PSV72.006c</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -11338,7 +11332,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>WC mísa závěsná + nádržka — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -11351,7 +11345,7 @@
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>1× WC (DXF)</t>
+          <t>1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
@@ -11377,7 +11371,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006b</t>
+          <t>PSV72.007</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -11397,7 +11391,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -11406,26 +11400,26 @@
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
-          <t>1× umyvadlo (TZ standard)</t>
+          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr"/>
@@ -11436,7 +11430,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006c</t>
+          <t>PSV72.008a</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -11456,7 +11450,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout + vanička — dodávka + montáž, koupelna 3.04 3.NP</t>
+          <t>Rohový ventil WC — dodávka + montáž</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -11465,11 +11459,11 @@
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>1× sprcha (TZ standard)</t>
+          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -11479,7 +11473,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
@@ -11495,7 +11489,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>PSV72.007</t>
+          <t>PSV72.008b</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -11515,7 +11509,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Páková umyvadlová baterie — dodávka + montáž</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -11524,26 +11518,26 @@
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
+          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr"/>
@@ -11554,7 +11548,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008a</t>
+          <t>PSV72.008c</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -11574,7 +11568,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Rohový ventil WC — dodávka + montáž</t>
+          <t>Sprchová / vanová baterie termostatická — dodávka + montáž</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -11587,7 +11581,7 @@
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>3× WC (1.NP + 2.NP + 3.NP)</t>
+          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -11613,7 +11607,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008b</t>
+          <t>PSV72.008d</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -11633,7 +11627,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Páková umyvadlová baterie — dodávka + montáž</t>
+          <t>Dřezová baterie kuchyňská — dodávka + montáž</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -11642,11 +11636,11 @@
         </is>
       </c>
       <c r="H187" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>3× umyvadlo (1.NP + 2.NP + 3.NP)</t>
+          <t>2× kuchyně (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -11672,7 +11666,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008c</t>
+          <t>PSV72.009</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -11692,7 +11686,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Sprchová / vanová baterie termostatická — dodávka + montáž</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -11701,26 +11695,26 @@
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>1× vana 1.NP + 2× sprcha 2.NP+3.NP</t>
+          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr"/>
@@ -11731,7 +11725,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>PSV72.008d</t>
+          <t>PSV72.010</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -11751,7 +11745,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Dřezová baterie kuchyňská — dodávka + montáž</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -11760,26 +11754,26 @@
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>2× kuchyně (1.06 + 3.05)</t>
+          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr"/>
@@ -11790,7 +11784,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>PSV72.009</t>
+          <t>PSV73.001</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -11800,17 +11794,17 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -11823,17 +11817,17 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
+          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -11849,7 +11843,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>PSV72.010</t>
+          <t>PSV73.002</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -11859,40 +11853,39 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I191" s="3" t="inlineStr">
-        <is>
-          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
-        </is>
+      <c r="I191" s="3">
+        <f> ks kamen</f>
+        <v/>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
@@ -11908,7 +11901,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>PSV73.001</t>
+          <t>PSV73.003</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -11928,7 +11921,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -11941,17 +11934,17 @@
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
+          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -11967,7 +11960,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>PSV73.002</t>
+          <t>PSV73.004</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -11987,29 +11980,30 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H193" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I193" s="3">
-        <f> ks kamen</f>
-        <v/>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
+        </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -12025,7 +12019,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>PSV73.003</t>
+          <t>PSV73.005</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -12045,7 +12039,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -12058,17 +12052,17 @@
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
+          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -12084,7 +12078,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>PSV73.004</t>
+          <t>PSV73.006</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -12104,7 +12098,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -12113,21 +12107,21 @@
         </is>
       </c>
       <c r="H195" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
+          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
@@ -12143,7 +12137,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>PSV73.005</t>
+          <t>PSV73.007</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -12163,12 +12157,12 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H196" s="2" t="n">
@@ -12176,17 +12170,17 @@
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
+          <t>TZ ARS — komín revize a úpravy stávajícího</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -12202,7 +12196,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>PSV73.006</t>
+          <t>PSV73.008</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -12222,30 +12216,30 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
+          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="L197" s="2" t="inlineStr">
@@ -12261,7 +12255,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>PSV73.007</t>
+          <t>M21.001</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -12271,17 +12265,17 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -12294,17 +12288,17 @@
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — komín revize a úpravy stávajícího</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -12320,7 +12314,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>PSV73.008</t>
+          <t>M21.002</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -12330,40 +12324,40 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
@@ -12379,7 +12373,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>M21.001</t>
+          <t>M21.003</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -12399,30 +12393,30 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -12438,7 +12432,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>M21.002</t>
+          <t>M21.004</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -12458,7 +12452,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -12467,21 +12461,21 @@
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
@@ -12497,7 +12491,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>M21.003</t>
+          <t>M21.005</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -12517,30 +12511,30 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>700</v>
+        <v>35</v>
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -12556,7 +12550,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>M21.004</t>
+          <t>M21.006</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -12576,30 +12570,30 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="L203" s="2" t="inlineStr">
@@ -12615,7 +12609,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>M21.005</t>
+          <t>M21.007</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -12635,30 +12629,30 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -12674,7 +12668,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>M21.006</t>
+          <t>VRN.001</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -12684,40 +12678,40 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="H205" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
@@ -12733,7 +12727,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>M21.007</t>
+          <t>VRN.002</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -12743,40 +12737,40 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>1 ks × 8 měs realizace</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -12792,7 +12786,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>VRN.001</t>
+          <t>VRN.003</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -12812,30 +12806,30 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H207" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
+          <t>Komplexní zřízení + provoz po dobu stavby</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -12851,7 +12845,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>VRN.002</t>
+          <t>VRN.101</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -12861,40 +12855,40 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>1 ks × 8 měs realizace</t>
+          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -12910,7 +12904,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>VRN.003</t>
+          <t>VRN.201</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -12920,17 +12914,17 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -12943,17 +12937,17 @@
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>Komplexní zřízení + provoz po dobu stavby</t>
+          <t>realizace ~8 měs</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -12969,7 +12963,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>VRN.101</t>
+          <t>VRN.301</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -12979,40 +12973,40 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
+          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -13028,7 +13022,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>VRN.201</t>
+          <t>VRN.302</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -13038,17 +13032,17 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -13061,17 +13055,17 @@
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>realizace ~8 měs</t>
+          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
@@ -13087,7 +13081,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>VRN.301</t>
+          <t>VRN.401</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -13097,22 +13091,22 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H212" s="2" t="n">
@@ -13120,17 +13114,17 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
+          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -13146,7 +13140,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>VRN.302</t>
+          <t>VRN.402</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -13156,17 +13150,17 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -13179,17 +13173,17 @@
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
+          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="L213" s="2" t="inlineStr">
@@ -13205,7 +13199,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>VRN.401</t>
+          <t>VRN.501</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -13215,17 +13209,17 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -13234,21 +13228,21 @@
         </is>
       </c>
       <c r="H214" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
+          <t>2 etapy geodet × 1 kpl</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -13264,7 +13258,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>VRN.402</t>
+          <t>VRN.601</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -13274,17 +13268,17 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -13297,17 +13291,17 @@
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
+          <t>Standard — DSP pro kolaudaci</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="L215" s="2" t="inlineStr">
@@ -13323,7 +13317,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>VRN.501</t>
+          <t>VRN.701</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -13333,17 +13327,17 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -13352,21 +13346,21 @@
         </is>
       </c>
       <c r="H216" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>2 etapy geodet × 1 kpl</t>
+          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -13382,7 +13376,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>VRN.601</t>
+          <t>VRN.801</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -13392,22 +13386,22 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H217" s="2" t="n">
@@ -13415,17 +13409,17 @@
       </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
-          <t>Standard — DSP pro kolaudaci</t>
+          <t>Standard — paušál kolaudace</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="L217" s="2" t="inlineStr">
@@ -13441,7 +13435,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>VRN.701</t>
+          <t>VRN.102</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -13451,22 +13445,22 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
@@ -13474,17 +13468,17 @@
       </c>
       <c r="I218" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
+          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -13500,7 +13494,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>VRN.801</t>
+          <t>VRN.103</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -13510,40 +13504,40 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>1</v>
+        <v>56.9</v>
       </c>
       <c r="I219" s="3" t="inlineStr">
         <is>
-          <t>Standard — paušál kolaudace</t>
+          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -13559,12 +13553,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>VRN.102</t>
+          <t>VRN.001</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -13579,12 +13573,12 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H220" s="2" t="n">
@@ -13592,17 +13586,17 @@
       </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
+          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -13618,12 +13612,12 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>VRN.103</t>
+          <t>VRN.002</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -13638,7 +13632,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -13647,11 +13641,11 @@
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>56.9</v>
+        <v>8</v>
       </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
+          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -13661,7 +13655,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="L221" s="2" t="inlineStr">
@@ -13677,7 +13671,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>VRN.001</t>
+          <t>VRN.101</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -13687,17 +13681,17 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -13710,17 +13704,17 @@
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
+          <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
@@ -13736,7 +13730,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>VRN.002</t>
+          <t>VRN.201</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -13746,40 +13740,40 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Společné</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Společné</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030001000</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
         </is>
       </c>
       <c r="L223" s="2" t="inlineStr">
@@ -13795,55 +13789,55 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>VRN.101</t>
+          <t>HSV6.013</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>Standard geodet vytýčení pro nový objekt</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>carried_verified</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr"/>
@@ -13854,55 +13848,55 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>VRN.201</t>
+          <t>HSV6.014</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>carried_verified</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr"/>
@@ -13913,7 +13907,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>HSV6.013</t>
+          <t>HSV6.015</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -13933,7 +13927,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -13942,26 +13936,26 @@
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr"/>
@@ -13972,7 +13966,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>HSV6.014</t>
+          <t>PSV76.013</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -13982,17 +13976,17 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -14001,26 +13995,26 @@
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I227" s="3" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr"/>
@@ -14031,7 +14025,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>HSV6.015</t>
+          <t>VRN.020</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -14041,40 +14035,40 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
@@ -14090,7 +14084,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>PSV76.013</t>
+          <t>PSV76.014</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -14110,7 +14104,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -14119,21 +14113,21 @@
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="L229" s="2" t="inlineStr">
@@ -14149,7 +14143,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>VRN.020</t>
+          <t>PSV72.004.A</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -14159,22 +14153,22 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H230" s="2" t="n">
@@ -14182,17 +14176,17 @@
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L230" s="2" t="inlineStr">
@@ -14208,7 +14202,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>PSV76.014</t>
+          <t>PSV72.004.B</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -14218,17 +14212,17 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -14237,21 +14231,21 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I231" s="3" t="inlineStr">
         <is>
-          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L231" s="2" t="inlineStr">
@@ -14267,7 +14261,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.A</t>
+          <t>PSV72.004.C</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -14287,7 +14281,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -14305,7 +14299,7 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -14326,7 +14320,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.B</t>
+          <t>PSV72.005.A</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -14346,7 +14340,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -14359,7 +14353,7 @@
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -14369,7 +14363,7 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L233" s="2" t="inlineStr">
@@ -14385,7 +14379,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>PSV72.004.C</t>
+          <t>PSV72.005.B</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -14405,7 +14399,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -14418,17 +14412,17 @@
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L234" s="2" t="inlineStr">
@@ -14444,7 +14438,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.A</t>
+          <t>PSV72.005.C</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -14464,7 +14458,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -14482,7 +14476,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -14503,7 +14497,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.B</t>
+          <t>PSV72.006.A</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -14523,7 +14517,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -14536,17 +14530,17 @@
       </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L236" s="2" t="inlineStr">
@@ -14562,7 +14556,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>PSV72.005.C</t>
+          <t>PSV72.006.B</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -14582,7 +14576,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -14595,17 +14589,17 @@
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="L237" s="2" t="inlineStr">
@@ -14621,7 +14615,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.A</t>
+          <t>PSV72.006.C</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -14641,7 +14635,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -14659,7 +14653,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -14680,7 +14674,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.B</t>
+          <t>PSV78.012.1_PP</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -14690,40 +14684,40 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H239" s="2" t="n">
-        <v>1</v>
+        <v>78.2</v>
       </c>
       <c r="I239" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="L239" s="2" t="inlineStr">
@@ -14739,7 +14733,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>PSV72.006.C</t>
+          <t>PSV78.012.1_NP</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -14749,40 +14743,40 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>1</v>
+        <v>254.5</v>
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -14798,7 +14792,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.1_PP</t>
+          <t>PSV78.012.2_NP</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -14818,7 +14812,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -14827,11 +14821,11 @@
         </is>
       </c>
       <c r="H241" s="2" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
-          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -14841,7 +14835,7 @@
       </c>
       <c r="K241" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="L241" s="2" t="inlineStr">
@@ -14857,7 +14851,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.1_NP</t>
+          <t>PSV78.012.3_NP</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -14877,7 +14871,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -14886,11 +14880,11 @@
         </is>
       </c>
       <c r="H242" s="2" t="n">
-        <v>254.5</v>
+        <v>219.3</v>
       </c>
       <c r="I242" s="3" t="inlineStr">
         <is>
-          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -14900,7 +14894,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="L242" s="2" t="inlineStr">
@@ -14916,7 +14910,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.2_NP</t>
+          <t>HSV6.016</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -14926,45 +14920,45 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>247.5</v>
+        <v>0.6</v>
       </c>
       <c r="I243" s="3" t="inlineStr">
         <is>
-          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="K243" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M243" s="2" t="inlineStr"/>
@@ -14975,7 +14969,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>PSV78.012.3_NP</t>
+          <t>HSV6.017</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -14985,45 +14979,45 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="H244" s="2" t="n">
-        <v>219.3</v>
+        <v>8</v>
       </c>
       <c r="I244" s="3" t="inlineStr">
         <is>
-          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>FAMILY_VERIFIED</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr"/>
@@ -15034,7 +15028,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>HSV6.016</t>
+          <t>HSV1.015a</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -15044,45 +15038,44 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H245" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="I245" s="3">
+        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <v/>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>212</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr"/>
@@ -15093,7 +15086,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>HSV6.017</t>
+          <t>HSV1.015b</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -15103,45 +15096,44 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="I246" s="3">
+        <f> HSV1.015 délka drenáže 12 m</f>
+        <v/>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>212</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>FAMILY_VERIFIED</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr"/>
@@ -15152,7 +15144,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015a</t>
+          <t>HSV1.015c</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -15172,7 +15164,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Drenážní trubka DN100 vlnitá perforovaná — uložení za opěrnou stěnou (bílou vanou)</t>
+          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -15184,12 +15176,12 @@
         <v>12</v>
       </c>
       <c r="I247" s="3">
-        <f> HSV1.015 obvod BV ~10 m + napojení 2 m = 12 m</f>
+        <f> HSV1.015 délka 12 m</f>
         <v/>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>693</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -15210,57 +15202,62 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015b</t>
+          <t>HSV5.001</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Štěrkový obsyp drenáže frakce 16/32 mm</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H248" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I248" s="3">
-        <f> HSV1.015 délka drenáže 12 m</f>
-        <v/>
+        <v>5.5</v>
+      </c>
+      <c r="I248" s="3" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
+        </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
-        </is>
-      </c>
-      <c r="M248" s="2" t="inlineStr"/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -15268,7 +15265,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>HSV1.015c</t>
+          <t>VRN.PM01</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -15278,44 +15275,41 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Geotextilie obalení drenáže + napojení do dešťové kanalizace</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>t</t>
         </is>
       </c>
       <c r="H249" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="I249" s="3">
-        <f> HSV1.015 délka 12 m</f>
-        <v/>
-      </c>
-      <c r="J249" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I249" s="3" t="inlineStr">
+        <is>
+          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 (drenáž za opěrnou stěnou) + POZN.2.02 z půdorysů návrh + řez A-A návrh</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M249" s="2" t="inlineStr"/>
@@ -15326,27 +15320,27 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>HSV5.001</t>
+          <t>VRN.PM02</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -15355,21 +15349,17 @@
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>5.5</v>
+        <v>503.1</v>
       </c>
       <c r="I250" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="J250" s="2" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
+          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -15377,11 +15367,7 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M250" s="2" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="M250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -15389,7 +15375,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>VRN.PM01</t>
+          <t>HSV1.016</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -15399,44 +15385,48 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I251" s="3" t="inlineStr">
         <is>
-          <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
+          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>Situace měření 2026-05-29 (rameno 8×175×280 + rameno 5×175×280) + TZ statika §3.2.5 'schody na terénu z betonových dílců do betonového lože'</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M251" s="2" t="inlineStr"/>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>Venkovní schody na terénu</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -15444,7 +15434,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>VRN.PM02</t>
+          <t>HSV5.017a</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -15454,44 +15444,51 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>503.1</v>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
-        </is>
-      </c>
-      <c r="J252" s="2" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="I252" s="3">
+        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
+        <v/>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>762085112</t>
+        </is>
+      </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M252" s="2" t="inlineStr"/>
+          <t>carried_verified</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -15499,7 +15496,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>HSV1.016</t>
+          <t>HSV5.017b</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -15509,46 +15506,49 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="H253" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I253" s="3" t="inlineStr">
-        <is>
-          <t>Situace měření 2026-05-29: rameno 1 = 8 stupňů + rameno 2 = 5 stupňů = 13 stupňů (175×280 mm)</t>
-        </is>
-      </c>
-      <c r="J253" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="I253" s="3">
+        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
+        <v/>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>31197004</t>
+        </is>
+      </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>Situace měření 2026-05-29 (rameno 8×175×280 + rameno 5×175×280) + TZ statika §3.2.5 'schody na terénu z betonových dílců do betonového lože'</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu</t>
+          <t>Krov — spojovací prostředky</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017a</t>
+          <t>HSV5.017c</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -15578,24 +15578,24 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Montáž svorníků/šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje kleštin 2×60/180 s krokvemi</t>
+          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>100 ks</t>
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I254" s="3">
-        <f> HSV5.017 počet svorníků 50 ks (11 pozic × 2 konce × 2)</f>
+        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
         <v/>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>762085112</t>
+          <t>3111006</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>carried_verified</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017b</t>
+          <t>HSV5.017d</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -15640,24 +15640,24 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Tyč závitová Pz 4.6 M12 — materiál svorníků krovu</t>
+          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>100 ks</t>
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I255" s="3">
-        <f> 50 ks × 0.25 m × 1.10 prořez = 13.75 → 14 m</f>
+        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
         <v/>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>31197004</t>
+          <t>31121004</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017c</t>
+          <t>HSV4.015a</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -15692,39 +15692,39 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Matice přesná šestihranná Pz DIN 934-8 M12</t>
+          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>100 ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H256" s="2" t="n">
-        <v>1</v>
+        <v>59.5</v>
       </c>
       <c r="I256" s="3">
-        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
+        <f> plocha stropu S07</f>
         <v/>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>3111006</t>
+          <t>713191</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
+          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
         </is>
       </c>
       <c r="L256" s="2" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="M256" s="2" t="inlineStr">
         <is>
-          <t>Krov — spojovací prostředky</t>
+          <t>S07</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>HSV5.017d</t>
+          <t>HSV4.015b</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -15754,49 +15754,45 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Podložka pod dřevěnou konstrukci DIN 440 D 12 mm</t>
+          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>100 ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H257" s="2" t="n">
-        <v>1</v>
+        <v>62.5</v>
       </c>
       <c r="I257" s="3">
-        <f> 50 svorníků × 2 = 100 ks = 1×100ks</f>
+        <f> 59.5 × 1.05 prořez</f>
         <v/>
       </c>
-      <c r="J257" s="2" t="inlineStr">
-        <is>
-          <t>31121004</t>
-        </is>
-      </c>
+      <c r="J257" s="2" t="inlineStr"/>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
+          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
         </is>
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>Krov — spojovací prostředky</t>
+          <t>S07</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15802,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>HSV4.015a</t>
+          <t>HSV4.016a</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15826,7 +15822,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Montáž kročejové izolace Isover T-P 30 mm — strop S07</t>
+          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -15835,25 +15831,21 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>59.5</v>
+        <v>65.5</v>
       </c>
       <c r="I258" s="3">
-        <f> plocha stropu S07</f>
+        <f> 59.5 × 1.10 přesahy</f>
         <v/>
       </c>
-      <c r="J258" s="2" t="inlineStr">
-        <is>
-          <t>713191</t>
-        </is>
-      </c>
+      <c r="J258" s="2" t="inlineStr"/>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
+          <t>skladba S07 návrh — separační geotextilie</t>
         </is>
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
@@ -15868,7 +15860,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>HSV4.015b</t>
+          <t>HSV4.017a</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -15888,7 +15880,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Deska kročejová Isover T-P 30 mm — materiál</t>
+          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -15897,26 +15889,30 @@
         </is>
       </c>
       <c r="H259" s="2" t="n">
-        <v>62.5</v>
+        <v>104.4</v>
       </c>
       <c r="I259" s="3">
-        <f> 59.5 × 1.05 prořez</f>
+        <f> plocha stropu S09</f>
         <v/>
       </c>
-      <c r="J259" s="2" t="inlineStr"/>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>713121</t>
+        </is>
+      </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — kročejová Isover T-P 30 mm</t>
+          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
         </is>
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S09</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15922,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>HSV4.016a</t>
+          <t>HSV4.017b</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -15946,7 +15942,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Separační geotextilie — dodávka + pokládka, strop S07</t>
+          <t>Minerální vata 180/200 mm — materiál</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -15955,16 +15951,16 @@
         </is>
       </c>
       <c r="H260" s="2" t="n">
-        <v>65.5</v>
+        <v>109.6</v>
       </c>
       <c r="I260" s="3">
-        <f> 59.5 × 1.10 přesahy</f>
+        <f> 104.4 × 1.05</f>
         <v/>
       </c>
       <c r="J260" s="2" t="inlineStr"/>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>skladba S07 návrh — separační geotextilie</t>
+          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
@@ -15974,7 +15970,7 @@
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S09</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15980,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>HSV4.017a</t>
+          <t>HSV4.018a</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -16004,7 +16000,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Montáž min. vaty mezi ocel. nosníky — strop S09</t>
+          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -16012,31 +16008,30 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H261" s="2" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="I261" s="3">
-        <f> plocha stropu S09</f>
-        <v/>
-      </c>
-      <c r="J261" s="2" t="inlineStr">
-        <is>
-          <t>713121</t>
-        </is>
-      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
+          <t>skladba S08 legenda (řez nepretíná, plocha nepřiřazena)</t>
         </is>
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S08</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16041,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>HSV4.017b</t>
+          <t>HSV4.019a</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -16066,7 +16061,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Minerální vata 180/200 mm — materiál</t>
+          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -16074,17 +16069,24 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H262" s="2" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="I262" s="3">
-        <f> 104.4 × 1.05</f>
-        <v/>
-      </c>
-      <c r="J262" s="2" t="inlineStr"/>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — V1</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>713191</t>
+        </is>
+      </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>skladba S09 návrh — min. vata výplň 180/200 mm</t>
+          <t>skladba S08 legenda</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
@@ -16094,7 +16096,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S08</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16106,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>HSV4.018a</t>
+          <t>HSV4.020a</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -16124,7 +16126,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Fermacell 2E22 25 mm — montáž+materiál, S08 (plocha neurčeno)</t>
+          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -16145,7 +16147,7 @@
       <c r="J263" s="2" t="inlineStr"/>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda (řez nepretíná, plocha nepřiřazena)</t>
+          <t>skladba S08 legenda</t>
         </is>
       </c>
       <c r="L263" s="2" t="inlineStr">
@@ -16165,7 +16167,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>HSV4.019a</t>
+          <t>HSV4.021a</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -16185,7 +16187,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Kročejová izolace 30 mm — montáž+materiál, S08 (neurčeno)</t>
+          <t>Separační vrstva — S08 (neurčeno)</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -16203,11 +16205,7 @@
           <t>neurčeno — V1</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr">
-        <is>
-          <t>713191</t>
-        </is>
-      </c>
+      <c r="J264" s="2" t="inlineStr"/>
       <c r="K264" s="3" t="inlineStr">
         <is>
           <t>skladba S08 legenda</t>
@@ -16230,7 +16228,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>HSV4.020a</t>
+          <t>HSV7.007a</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -16240,17 +16238,17 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Suchý podsyp keramzit/liapor + dřevěný rošt 50 mm — S08 (neurčeno)</t>
+          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -16258,20 +16256,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H265" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I265" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — V1</t>
-        </is>
+      <c r="H265" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I265" s="3">
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <v/>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="L265" s="2" t="inlineStr">
@@ -16281,7 +16276,7 @@
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16286,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>HSV4.021a</t>
+          <t>HSV7.007b</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -16301,17 +16296,17 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Separační vrstva — S08 (neurčeno)</t>
+          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -16319,20 +16314,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H266" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I266" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — V1</t>
-        </is>
+      <c r="H266" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I266" s="3">
+        <f> 23 × 1.05</f>
+        <v/>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>skladba S08 legenda</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -16342,7 +16334,7 @@
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16344,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>HSV7.007a</t>
+          <t>HSV7.008a</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16372,7 +16364,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Montáž sanační izolační desky Styrcon 200 + armovací — sokl S03</t>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -16381,16 +16373,16 @@
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I267" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> 23 × 1.10</f>
         <v/>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>Řez A-A/C-C sokl + obvod ETICS</t>
         </is>
       </c>
       <c r="L267" s="2" t="inlineStr">
@@ -16410,7 +16402,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>HSV7.007b</t>
+          <t>HSV7.009a</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -16430,7 +16422,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Sanační deska Styrcon 200 + lepící tmel + armovací stěrka+tkanina — materiál</t>
+          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -16439,16 +16431,16 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I268" s="3">
-        <f> 23 × 1.05</f>
+        <f> 23 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -16468,7 +16460,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>HSV7.008a</t>
+          <t>HSV7.009b</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -16488,7 +16480,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Drenážní nopová folie 20 mm — dodávka+montáž, sokl pod terénem S03a</t>
+          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -16497,21 +16489,25 @@
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I269" s="3">
-        <f> 23 × 1.10</f>
+        <f> 23 × 1.05</f>
         <v/>
       </c>
-      <c r="J269" s="2" t="inlineStr"/>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A/C-C sokl + obvod ETICS</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>needs_lookup</t>
+          <t>family_only</t>
         </is>
       </c>
       <c r="M269" s="2" t="inlineStr">
@@ -16526,7 +16522,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>HSV7.009a</t>
+          <t>HSV5.018a</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -16536,17 +16532,17 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Kotevní rošt 40 mm provětraného soklu — montáž+materiál S03b</t>
+          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -16555,16 +16551,16 @@
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="I270" s="3">
-        <f> 23 (OVĚŘIT)</f>
+        <f> 140.94 × 1.10 přesahy</f>
         <v/>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>skladba S10 návrh — pojistná HI pod Al krytinu</t>
         </is>
       </c>
       <c r="L270" s="2" t="inlineStr">
@@ -16574,7 +16570,7 @@
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S10</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16580,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>HSV7.009b</t>
+          <t>HSV6.018a</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -16594,17 +16590,17 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Keramický obklad soklu 20 mm — montáž+materiál</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -16613,25 +16609,21 @@
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I271" s="3">
-        <f> 23 × 1.05</f>
+        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
         <v/>
       </c>
-      <c r="J271" s="2" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
+      <c r="J271" s="2" t="inlineStr"/>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
         </is>
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>family_only</t>
+          <t>needs_lookup</t>
         </is>
       </c>
       <c r="M271" s="2" t="inlineStr">
@@ -16646,27 +16638,27 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>HSV5.018a</t>
+          <t>HSV5.002a</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV 5 Komunikace pozemní — dlažby</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Pojistná HI folie pod Al krytinu — dodávka+montáž S10</t>
+          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -16674,17 +16666,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H272" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="I272" s="3">
-        <f> 140.94 × 1.10 přesahy</f>
-        <v/>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
+        </is>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>skladba S10 návrh — pojistná HI pod Al krytinu</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="L272" s="2" t="inlineStr">
@@ -16692,11 +16687,7 @@
           <t>needs_lookup</t>
         </is>
       </c>
-      <c r="M272" s="2" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+      <c r="M272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -16704,27 +16695,27 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>HSV6.018a</t>
+          <t>HSV5.002b</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV 5 Komunikace pozemní — dlažby</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (sokl) 20 mm</t>
+          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -16732,17 +16723,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="H273" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I273" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
-        <v/>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>neurčeno</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>neurčeno — OVĚŘIT</t>
+        </is>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
       <c r="K273" s="3" t="inlineStr">
         <is>
-          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="L273" s="2" t="inlineStr">
@@ -16750,11 +16744,7 @@
           <t>needs_lookup</t>
         </is>
       </c>
-      <c r="M273" s="2" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
+      <c r="M273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -16762,7 +16752,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002a</t>
+          <t>HSV5.002c</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -16782,12 +16772,12 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Betonová dlažba napojení vjezdu na komunikaci Dvořákova</t>
+          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -16797,7 +16787,7 @@
       </c>
       <c r="I274" s="3" t="inlineStr">
         <is>
-          <t>neurčeno — situace C.3.R1 OVĚŘIT</t>
+          <t>neurčeno — OVĚŘIT</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
@@ -16819,7 +16809,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002b</t>
+          <t>PSV76.002a</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -16829,38 +16819,35 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>HSV 5 Komunikace pozemní — dlažby</t>
+          <t>PSV 767 zámečnické konstrukce</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Podkladní vrstva kameniva pod dlažbu vjezdu</t>
+          <t>Vjezdová brána ocelová — dodávka + montáž</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H275" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" s="3">
+        <f> 1 brána</f>
+        <v/>
       </c>
       <c r="J275" s="2" t="inlineStr"/>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="L275" s="2" t="inlineStr">
@@ -16876,7 +16863,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>HSV5.002c</t>
+          <t>VRN.003a</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -16886,17 +16873,17 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>VRN — Geodet / PČR</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>HSV 5 Komunikace pozemní — dlažby</t>
+          <t>VRN geodetické + zaměřovací práce</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Spádování + odvodnění dešťové vody na pozemek investora</t>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -16904,20 +16891,17 @@
           <t>soubor</t>
         </is>
       </c>
-      <c r="H276" s="4" t="inlineStr">
-        <is>
-          <t>neurčeno</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>neurčeno — OVĚŘIT</t>
-        </is>
+      <c r="H276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" s="3">
+        <f> 1 soubor</f>
+        <v/>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
         </is>
       </c>
       <c r="L276" s="2" t="inlineStr">
@@ -16933,27 +16917,27 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>PSV76.002a</t>
+          <t>M24.001a</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>PSV 767 zámečnické konstrukce</t>
+          <t>M / 751 vzduchotechnika — odtah digestoře</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Vjezdová brána ocelová — dodávka + montáž</t>
+          <t>Lokální odtah digestoře kuchyně + prostup + zpětná klapka</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -16962,16 +16946,16 @@
         </is>
       </c>
       <c r="H277" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I277" s="3">
-        <f> 1 brána</f>
+        <f> 2 kuchyně (1.NP + 3.NP)</f>
         <v/>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
       <c r="K277" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="L277" s="2" t="inlineStr">
@@ -16987,27 +16971,27 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>VRN.003a</t>
+          <t>M21.008a</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>VRN geodetické + zaměřovací práce</t>
+          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40, Dz=25 m)</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -17025,7 +17009,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr">
@@ -17041,7 +17025,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>M24.001a</t>
+          <t>M21.008b</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -17051,35 +17035,35 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>M-24 VZT</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>M / 751 vzduchotechnika — odtah digestoře</t>
+          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Lokální odtah digestoře kuchyně + prostup + zpětná klapka</t>
+          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="H279" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I279" s="3">
-        <f> 2 kuchyně (1.NP + 3.NP)</f>
+        <f> 1 soubor</f>
         <v/>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
       <c r="K279" s="3" t="inlineStr">
         <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="L279" s="2" t="inlineStr">
@@ -17095,7 +17079,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>M21.008a</t>
+          <t>PSV95.003a</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -17105,17 +17089,17 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
+          <t>VRN doklady / revize požární</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -17133,7 +17117,7 @@
       <c r="J280" s="2" t="inlineStr"/>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="L280" s="2" t="inlineStr">
@@ -17143,116 +17127,8 @@
       </c>
       <c r="M280" s="2" t="inlineStr"/>
     </row>
-    <row r="281">
-      <c r="A281" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>M21.008b</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>M-21 ELI silnoproud</t>
-        </is>
-      </c>
-      <c r="E281" s="3" t="inlineStr">
-        <is>
-          <t>M 21 elektroinstalace — hlavní vypínač + značení</t>
-        </is>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>Požární značení rozvodů + uzávěrů (voda/elektro)</t>
-        </is>
-      </c>
-      <c r="G281" s="2" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="H281" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I281" s="3">
-        <f> 1 soubor</f>
-        <v/>
-      </c>
-      <c r="J281" s="2" t="inlineStr"/>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
-        </is>
-      </c>
-      <c r="L281" s="2" t="inlineStr">
-        <is>
-          <t>needs_lookup</t>
-        </is>
-      </c>
-      <c r="M281" s="2" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
-        <v>281</v>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>PSV95.003a</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>PSV-95 Detekce požární</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="inlineStr">
-        <is>
-          <t>VRN doklady / revize požární</t>
-        </is>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="H282" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I282" s="3">
-        <f> 1 soubor</f>
-        <v/>
-      </c>
-      <c r="J282" s="2" t="inlineStr"/>
-      <c r="K282" s="3" t="inlineStr">
-        <is>
-          <t>PBŘ D.3</t>
-        </is>
-      </c>
-      <c r="L282" s="2" t="inlineStr">
-        <is>
-          <t>needs_lookup</t>
-        </is>
-      </c>
-      <c r="M282" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M282"/>
+  <autoFilter ref="A1:M280"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATOMIC_FLAT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATOMIC_FLAT'!$A$1:$M$283</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M280"/>
+  <dimension ref="A1:M283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>podlaha sklad 21.2 m² × 0.15 m štěrku</t>
+          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2837,11 +2837,11 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>21.2 × 0.10 = 2.12</t>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>33.9</v>
+        <v>36.74</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>rozpon 3.34 × počet stropnic (6.35/0.625 = 10) = ~10 ks × 3.34 = 33.4</t>
+          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -16257,10 +16257,10 @@
         </is>
       </c>
       <c r="H265" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I265" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> obvod 38.7 × 0.6 × řadovka 0.7 ≈ 16 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
@@ -16315,10 +16315,10 @@
         </is>
       </c>
       <c r="H266" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I266" s="3">
-        <f> 23 × 1.05</f>
+        <f> 16 × 1.05</f>
         <v/>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
@@ -16373,10 +16373,10 @@
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I267" s="3">
-        <f> 23 × 1.10</f>
+        <f> 16 × 1.10</f>
         <v/>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
@@ -16431,10 +16431,10 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I268" s="3">
-        <f> 23 (OVĚŘIT)</f>
+        <f> 16 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
@@ -16489,10 +16489,10 @@
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I269" s="3">
-        <f> 23 × 1.05</f>
+        <f> 16 × 1.05</f>
         <v/>
       </c>
       <c r="J269" s="2" t="inlineStr">
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I271" s="3">
-        <f> obvod 38.7 × 0.6 ≈ 23 (OVĚŘIT)</f>
+        <f> obvod 38.7 × 0.6 × řadovka 0.7 ≈ 16 (OVĚŘIT)</f>
         <v/>
       </c>
       <c r="J271" s="2" t="inlineStr"/>
@@ -17127,8 +17127,182 @@
       </c>
       <c r="M280" s="2" t="inlineStr"/>
     </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>HSV3.004a</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>ÚRS 711 izolace proti vodě + protiradon</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>Asfaltová penetrace obvodových + opěrné stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I281" s="3">
+        <f> plocha stěn pod terénem 33 m² (OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>HSV3.004b</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>ÚRS 711 izolace proti vodě + protiradon</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>2× HI a protiradonový pás z modif. asfaltu 2×4 mm — stěny pod terénem</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I282" s="3">
+        <f> 33 m² (2 vrstvy ve spotřebě)</f>
+        <v/>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>HSV3.005a</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>ÚRS 711 nopová folie drenážní</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>Drenážní nopová folie 20 mm — dodávka+montáž, stěny pod terénem (S03a+S04)</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="I283" s="3">
+        <f> 33 × 1.10 přesahy</f>
+        <v/>
+      </c>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>needs_lookup</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M280"/>
+  <autoFilter ref="A1:M283"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>odhad — výška ~1.6 m × šíře 6.35 m / blok 0.8×0.4 = ~32 bloků × 2 řady = 64; round 60</t>
+          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — Herkul H-BLOK, montáž auto s hyd. rukou</t>
+          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -3955,11 +3955,11 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² ÷ 1.08 m²/blok (H-BLOK Standard 1800×600mm líc, web-ověřeno) = 17.6 → 18 ks; layout: 4 bloky/řada × 5 řad = 20 ks (s řezy) — použito 18 ks plocha-přesné</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m² ÷ 1.08 m²/blok (H-BLOK Standard 1800×600mm líc, web-ověřeno) = 17.6 → 18 ks; layout: 4 bloky/řada × 5 řad = 20 ks (s řezy) — použito 18 ks plocha-přesné</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/ATOMIC_FLAT_2026-06-01.xlsx
@@ -3955,11 +3955,11 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
